--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,65 +13,65 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="97">
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
   <si>
     <t>Project</t>
   </si>
   <si>
-    <t>How to fill the Projects sheet</t>
-  </si>
-  <si>
-    <t>Setting</t>
+    <t>Value</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
+    <t>BUA</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t>Company Name</t>
+    <t>Currency</t>
   </si>
   <si>
     <t>Phase</t>
   </si>
   <si>
-    <t>Alahly Sabbour</t>
+    <t>EGP</t>
   </si>
   <si>
     <t>Plan</t>
   </si>
   <si>
-    <t>Currency</t>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
     <t>Years</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
     <t>Discount %</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
@@ -81,78 +81,78 @@
     <t>Installments Count</t>
   </si>
   <si>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
+  </si>
+  <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
-    <t>Maintenance %</t>
+    <t>Delivery (months)</t>
   </si>
   <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
     <t>Column</t>
   </si>
   <si>
     <t>Meaning / المعنى</t>
   </si>
   <si>
-    <t>Ending Installment Maintenance Due (months)</t>
+    <t>Maintenance Basis</t>
+  </si>
+  <si>
+    <t>YOUD</t>
   </si>
   <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>Maintenance Basis</t>
-  </si>
-  <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
+  </si>
+  <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+  </si>
+  <si>
+    <t>Number of equal installments / عدد الأقساط</t>
+  </si>
+  <si>
     <t>Original Price</t>
   </si>
   <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
-  </si>
-  <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
@@ -174,21 +174,21 @@
     <t>% of system price, due at delivery / وديعة الصيانة</t>
   </si>
   <si>
+    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
+  </si>
+  <si>
+    <t>After editing: save the file, then refresh the page in the browser.</t>
+  </si>
+  <si>
+    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
+  </si>
+  <si>
     <t>Selling price</t>
   </si>
   <si>
-    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
-  </si>
-  <si>
     <t>10% DP &amp; 8 Years</t>
   </si>
   <si>
-    <t>After editing: save the file, then refresh the page in the browser.</t>
-  </si>
-  <si>
-    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
-  </si>
-  <si>
     <t>7.5% DP &amp; 7.5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>GAIA</t>
+  </si>
+  <si>
+    <t>SUMMER</t>
   </si>
 </sst>
 </file>
@@ -600,22 +603,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -624,7 +627,7 @@
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>19</v>
@@ -636,39 +639,39 @@
         <v>21</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +680,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -715,15 +718,15 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F3" s="1">
         <v>8.0</v>
@@ -732,7 +735,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -770,12 +773,12 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>58</v>
@@ -787,7 +790,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -825,12 +828,12 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>59</v>
@@ -842,7 +845,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -879,12 +882,12 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>60</v>
@@ -896,7 +899,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -933,12 +936,12 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>61</v>
@@ -950,7 +953,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -987,12 +990,12 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>62</v>
@@ -1004,7 +1007,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1041,12 +1044,12 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>63</v>
@@ -1058,7 +1061,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1095,12 +1098,12 @@
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>64</v>
@@ -1112,7 +1115,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1149,12 +1152,12 @@
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>65</v>
@@ -1169,7 +1172,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1205,12 +1208,12 @@
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1225,7 +1228,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1262,7 +1265,7 @@
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -1270,7 +1273,7 @@
         <v>67</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1279,7 +1282,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1317,7 +1320,7 @@
         <v>6.0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1328,7 @@
         <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F14" s="1">
         <v>8.0</v>
@@ -1334,7 +1337,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1372,7 +1375,7 @@
         <v>6.0</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -1389,7 +1392,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1427,7 +1430,7 @@
         <v>6.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -1444,7 +1447,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1482,7 +1485,7 @@
         <v>6.0</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
@@ -1499,7 +1502,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1537,7 +1540,7 @@
         <v>6.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -1554,7 +1557,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1592,7 +1595,7 @@
         <v>6.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -1609,7 +1612,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1647,7 +1650,7 @@
         <v>6.0</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
@@ -1664,7 +1667,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1702,7 +1705,7 @@
         <v>6.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
@@ -1719,7 +1722,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1757,7 +1760,7 @@
         <v>6.0</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
@@ -1774,7 +1777,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1812,7 +1815,7 @@
         <v>6.0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -1829,7 +1832,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1865,7 +1868,7 @@
         <v>3.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
@@ -1882,7 +1885,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -1918,7 +1921,7 @@
         <v>3.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
@@ -1935,7 +1938,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -1971,7 +1974,7 @@
         <v>3.0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
@@ -1988,7 +1991,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2024,7 +2027,7 @@
         <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
@@ -2041,7 +2044,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2077,7 +2080,7 @@
         <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
@@ -2094,7 +2097,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2130,7 +2133,7 @@
         <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -2147,7 +2150,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2183,7 +2186,7 @@
         <v>3.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -2200,7 +2203,7 @@
         <v>15.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I30" s="1">
         <v>100.0</v>
@@ -2236,7 +2239,7 @@
         <v>3.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -2253,7 +2256,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2290,7 +2293,7 @@
         <v>3.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
@@ -2307,7 +2310,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2343,7 +2346,7 @@
         <v>3.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
@@ -2360,7 +2363,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2396,7 +2399,7 @@
         <v>3.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -2413,7 +2416,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2449,7 +2452,7 @@
         <v>3.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
@@ -2466,7 +2469,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2502,7 +2505,7 @@
         <v>3.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
@@ -2519,7 +2522,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2555,7 +2558,7 @@
         <v>3.0</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37">
@@ -2572,7 +2575,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2608,7 +2611,7 @@
         <v>3.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
@@ -2625,7 +2628,7 @@
         <v>15.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I38" s="3">
         <v>100.0</v>
@@ -2661,7 +2664,7 @@
         <v>3.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
@@ -2681,7 +2684,7 @@
         <v>25.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I39" s="1">
         <v>100.0</v>
@@ -2717,7 +2720,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -2734,7 +2737,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2770,7 +2773,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -2787,7 +2790,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2823,7 +2826,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -2840,7 +2843,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -2876,7 +2879,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -2893,7 +2896,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -2929,7 +2932,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -2949,7 +2952,7 @@
         <v>25.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I44" s="1">
         <v>100.0</v>
@@ -2985,7 +2988,7 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45">
@@ -3005,7 +3008,7 @@
         <v>0.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I45" s="1">
         <v>5.0</v>
@@ -3041,7 +3044,7 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
@@ -3061,7 +3064,7 @@
         <v>3.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I46" s="1">
         <v>5.0</v>
@@ -3097,7 +3100,7 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -3117,7 +3120,7 @@
         <v>6.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I47" s="1">
         <v>5.0</v>
@@ -3153,7 +3156,7 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -3173,7 +3176,7 @@
         <v>9.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I48" s="1">
         <v>5.0</v>
@@ -3209,7 +3212,7 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
@@ -3217,7 +3220,7 @@
         <v>93</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3226,7 +3229,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3263,12 +3266,12 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F50" s="1">
         <v>8.0</v>
@@ -3277,7 +3280,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3314,7 +3317,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -3328,7 +3331,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3365,7 +3368,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -3379,7 +3382,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3416,7 +3419,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -3430,7 +3433,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3467,7 +3470,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -3481,7 +3484,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3518,7 +3521,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -3532,7 +3535,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3569,7 +3572,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
@@ -3583,7 +3586,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3620,7 +3623,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -3634,7 +3637,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3671,7 +3674,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
@@ -3685,7 +3688,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3722,7 +3725,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
@@ -3730,7 +3733,7 @@
         <v>94</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3739,7 +3742,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3775,12 +3778,12 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F60" s="1">
         <v>8.0</v>
@@ -3789,7 +3792,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3825,7 +3828,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -3839,7 +3842,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3875,7 +3878,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
@@ -3889,7 +3892,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3925,7 +3928,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
@@ -3939,7 +3942,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3975,7 +3978,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
@@ -3989,7 +3992,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4025,7 +4028,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -4039,7 +4042,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4075,7 +4078,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
@@ -4089,7 +4092,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4125,7 +4128,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67">
@@ -4139,7 +4142,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4175,7 +4178,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
@@ -4189,7 +4192,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4225,7 +4228,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69">
@@ -4233,7 +4236,7 @@
         <v>95</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4242,7 +4245,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4278,12 +4281,12 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
       <c r="E70" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F70" s="1">
         <v>8.0</v>
@@ -4292,7 +4295,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4328,7 +4331,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71">
@@ -4342,7 +4345,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4378,7 +4381,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72">
@@ -4392,7 +4395,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4428,7 +4431,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -4442,7 +4445,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4478,7 +4481,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
@@ -4492,7 +4495,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4528,7 +4531,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
@@ -4542,7 +4545,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4578,7 +4581,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76">
@@ -4592,7 +4595,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4628,7 +4631,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77">
@@ -4642,7 +4645,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4678,7 +4681,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
@@ -4692,7 +4695,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4728,7 +4731,520 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I79" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J79" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="K79" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L79" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O79" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P79" s="1">
+        <f t="shared" ref="P79:P88" si="6">4*12</f>
+        <v>48</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R79" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S79" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T79" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="E80" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F80" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G80" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I80" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J80" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K80" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L80" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="O80" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P80" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R80" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S80" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T80" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="E81" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F81" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G81" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I81" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="J81" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K81" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L81" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O81" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P81" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S81" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T81" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="E82" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F82" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G82" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I82" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J82" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K82" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L82" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M82" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N82" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O82" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P82" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R82" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S82" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T82" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="E83" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F83" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G83" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I83" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="J83" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="K83" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L83" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M83" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N83" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O83" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P83" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R83" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S83" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T83" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="E84" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F84" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G84" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I84" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J84" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="K84" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L84" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M84" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N84" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O84" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P84" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R84" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S84" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="E85" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F85" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G85" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I85" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="J85" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="K85" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L85" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M85" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N85" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O85" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P85" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q85" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R85" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S85" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T85" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="E86" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F86" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G86" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I86" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J86" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K86" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L86" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M86" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N86" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O86" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P86" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q86" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R86" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S86" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T86" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="E87" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F87" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G87" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I87" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="J87" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="K87" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L87" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M87" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N87" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O87" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P87" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q87" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R87" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S87" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T87" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="E88" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I88" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="J88" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="K88" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L88" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M88" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N88" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O88" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P88" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q88" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R88" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="S88" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -4753,26 +5269,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5797,15 +6313,15 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
@@ -5813,20 +6329,20 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>29</v>
@@ -5834,31 +6350,31 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>37</v>
@@ -5866,7 +6382,7 @@
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>38</v>
@@ -5877,15 +6393,15 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -5893,7 +6409,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -5901,7 +6417,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -5909,12 +6425,12 @@
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
@@ -5922,7 +6438,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>47</v>
@@ -5946,7 +6462,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>52</v>
@@ -5954,26 +6470,26 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,68 +13,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="107">
+  <si>
+    <t>Project</t>
+  </si>
   <si>
     <t>Setting</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Company Name</t>
   </si>
   <si>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t/>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Plan</t>
   </si>
   <si>
     <t>Currency</t>
   </si>
   <si>
-    <t>Phase</t>
-  </si>
-  <si>
     <t>EGP</t>
   </si>
   <si>
-    <t>Plan</t>
+    <t>Years</t>
   </si>
   <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>Years</t>
-  </si>
-  <si>
     <t>Discount %</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
+    <t>Down Payment 2 %</t>
+  </si>
+  <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
-    <t>Down Payment 2 %</t>
-  </si>
-  <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
@@ -87,27 +87,27 @@
     <t>First Installment Due (months)</t>
   </si>
   <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
     <t>Maintenance %</t>
   </si>
   <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
-  </si>
-  <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
     <t>Delivery (months)</t>
   </si>
   <si>
+    <t>First Installment Maintenance Due (months)</t>
+  </si>
+  <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
@@ -129,9 +129,15 @@
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
+    <t>Original Price</t>
+  </si>
+  <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
@@ -141,18 +147,12 @@
     <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
     <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
     <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
@@ -304,6 +304,36 @@
   </si>
   <si>
     <t>SUMMER</t>
+  </si>
+  <si>
+    <t>YOUD-TEST</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>10% DP &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>7.5% DP &amp; 7.5% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>10% DP &amp; 10% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>12.5% DP &amp; 12.5% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>15% DP &amp; 15% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>17.5% DP &amp; 17.5% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>20% DP &amp; 20% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>22.5% DP &amp; 22.5% After 3 Months &amp; 10 Years</t>
   </si>
 </sst>
 </file>
@@ -603,22 +633,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -627,10 +657,10 @@
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>20</v>
@@ -645,13 +675,13 @@
         <v>23</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>31</v>
@@ -671,7 +701,7 @@
         <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -680,7 +710,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -735,7 +765,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -790,7 +820,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -845,7 +875,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -899,7 +929,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -953,7 +983,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1007,7 +1037,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1061,7 +1091,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1115,7 +1145,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1172,7 +1202,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1228,7 +1258,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1273,7 +1303,7 @@
         <v>67</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1282,7 +1312,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1337,7 +1367,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1392,7 +1422,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1447,7 +1477,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1502,7 +1532,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1557,7 +1587,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1612,7 +1642,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1667,7 +1697,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1722,7 +1752,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1777,7 +1807,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1832,7 +1862,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1885,7 +1915,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -1938,7 +1968,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -1991,7 +2021,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2044,7 +2074,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2097,7 +2127,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2150,7 +2180,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2256,7 +2286,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2310,7 +2340,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2363,7 +2393,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2416,7 +2446,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2469,7 +2499,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2522,7 +2552,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2575,7 +2605,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2720,7 +2750,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -2737,7 +2767,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2773,7 +2803,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -2790,7 +2820,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2826,7 +2856,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -2843,7 +2873,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -2879,7 +2909,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -2896,7 +2926,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -2932,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -3220,7 +3250,7 @@
         <v>93</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3229,7 +3259,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3266,7 +3296,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
@@ -3280,7 +3310,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3317,7 +3347,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
@@ -3331,7 +3361,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3368,7 +3398,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -3382,7 +3412,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3419,7 +3449,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -3433,7 +3463,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3470,7 +3500,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -3484,7 +3514,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3521,7 +3551,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -3535,7 +3565,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3572,7 +3602,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
@@ -3586,7 +3616,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3623,7 +3653,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -3637,7 +3667,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3674,7 +3704,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -3688,7 +3718,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3725,7 +3755,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -3733,7 +3763,7 @@
         <v>94</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3742,7 +3772,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3778,7 +3808,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
@@ -3792,7 +3822,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3828,7 +3858,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
@@ -3842,7 +3872,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3878,7 +3908,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
@@ -3892,7 +3922,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3928,7 +3958,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -3942,7 +3972,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3978,7 +4008,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -3992,7 +4022,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4028,7 +4058,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -4042,7 +4072,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4078,7 +4108,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66">
@@ -4092,7 +4122,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4128,7 +4158,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67">
@@ -4142,7 +4172,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4178,7 +4208,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -4192,7 +4222,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4228,7 +4258,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -4236,7 +4266,7 @@
         <v>95</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4245,7 +4275,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4281,7 +4311,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70">
@@ -4295,7 +4325,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4331,7 +4361,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -4345,7 +4375,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4381,7 +4411,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -4395,7 +4425,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4431,7 +4461,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
@@ -4445,7 +4475,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4481,7 +4511,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
@@ -4495,7 +4525,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4531,7 +4561,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -4545,7 +4575,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4581,7 +4611,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -4595,7 +4625,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4631,7 +4661,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
@@ -4645,7 +4675,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4681,7 +4711,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -4695,7 +4725,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4731,7 +4761,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -4739,7 +4769,7 @@
         <v>96</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -4748,7 +4778,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -4772,7 +4802,7 @@
         <v>10.0</v>
       </c>
       <c r="P79" s="1">
-        <f t="shared" ref="P79:P88" si="6">4*12</f>
+        <f t="shared" ref="P79:P91" si="6">4*12</f>
         <v>48</v>
       </c>
       <c r="Q79" s="1">
@@ -4785,7 +4815,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -4799,7 +4829,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -4836,7 +4866,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81">
@@ -4850,7 +4880,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -4887,7 +4917,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82">
@@ -4901,7 +4931,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -4938,7 +4968,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">
@@ -4952,7 +4982,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -4989,7 +5019,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84">
@@ -5003,7 +5033,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5040,7 +5070,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
@@ -5054,7 +5084,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5091,7 +5121,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
@@ -5105,7 +5135,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5142,7 +5172,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -5156,7 +5186,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5193,7 +5223,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
@@ -5207,7 +5237,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5244,7 +5274,612 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F89" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I89" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="K89" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L89" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M89" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N89" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O89" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P89" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q89" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R89" s="1">
+        <f t="shared" ref="R89:R97" si="7">P89-6</f>
+        <v>42</v>
+      </c>
+      <c r="S89" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T89" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F90" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I90" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J90" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K90" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L90" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="M90" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N90" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="O90" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P90" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q90" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R90" s="1">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="S90" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T90" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I91" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="J91" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K91" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L91" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M91" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N91" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O91" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P91" s="1">
+        <f t="shared" si="6"/>
+        <v>48</v>
+      </c>
+      <c r="Q91" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R91" s="1">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="S91" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T91" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F92" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I92" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J92" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K92" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L92" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M92" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N92" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O92" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="R92" s="1">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="S92" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F93" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I93" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="J93" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="K93" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L93" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M93" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N93" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O93" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="R93" s="1">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="S93" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F94" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I94" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J94" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="K94" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L94" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M94" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N94" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O94" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="R94" s="1">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="S94" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T94" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F95" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I95" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="J95" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="K95" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L95" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M95" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N95" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O95" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P95" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="Q95" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="R95" s="1">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="S95" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T95" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F96" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I96" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J96" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K96" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L96" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M96" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N96" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O96" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="R96" s="1">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="S96" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T96" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F97" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I97" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="J97" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="K97" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L97" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M97" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N97" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O97" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="R97" s="1">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="S97" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T97" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I98" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="J98" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="K98" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M98" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N98" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O98" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P98" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="S98" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T98" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I99" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="J99" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="K99" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L99" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M99" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N99" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O99" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P99" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="R99" s="1">
+        <f>P99-6</f>
+        <v>30</v>
+      </c>
+      <c r="S99" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T99" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5269,7 +5904,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -5280,15 +5915,15 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -6310,31 +6945,31 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
@@ -6342,18 +6977,18 @@
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -6366,7 +7001,7 @@
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>36</v>
@@ -6374,7 +7009,7 @@
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>37</v>
@@ -6382,10 +7017,10 @@
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -6393,23 +7028,23 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -6417,7 +7052,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -6425,7 +7060,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -6462,7 +7097,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>52</v>
@@ -6478,10 +7113,10 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,142 +15,142 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="107">
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
     <t>Project</t>
   </si>
   <si>
-    <t>Setting</t>
+    <t>Value</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>How to fill the Projects sheet</t>
-  </si>
-  <si>
     <t>Company Name</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>BUA</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
     <t>Phase</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
     <t>Plan</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>EGP</t>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
     <t>Years</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
     <t>Discount %</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
     <t>Installments Count</t>
   </si>
   <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
     <t>Installment Every (months)</t>
   </si>
   <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
     <t>First Installment Due (months)</t>
   </si>
   <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
     <t>Maintenance %</t>
   </si>
   <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
     <t>Delivery (months)</t>
   </si>
   <si>
+    <t>Column</t>
+  </si>
+  <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+    <t>Meaning / المعنى</t>
   </si>
   <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+  </si>
+  <si>
     <t>YOUD</t>
   </si>
   <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
-  </si>
-  <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
+  </si>
+  <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
+  </si>
+  <si>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+  </si>
+  <si>
+    <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
     <t>Original Price</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
-  </si>
-  <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
@@ -633,22 +633,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -657,10 +657,10 @@
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>20</v>
@@ -669,39 +669,39 @@
         <v>21</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -710,7 +710,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>57</v>
@@ -765,7 +765,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>58</v>
@@ -820,7 +820,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>59</v>
@@ -875,7 +875,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>60</v>
@@ -929,7 +929,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>61</v>
@@ -983,7 +983,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>62</v>
@@ -1037,7 +1037,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>63</v>
@@ -1091,7 +1091,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1133,7 +1133,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>64</v>
@@ -1145,7 +1145,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>65</v>
@@ -1202,7 +1202,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1258,7 +1258,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1303,7 +1303,7 @@
         <v>67</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1312,7 +1312,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1367,7 +1367,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1422,7 +1422,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1477,7 +1477,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1532,7 +1532,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1587,7 +1587,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1642,7 +1642,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1697,7 +1697,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1752,7 +1752,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1807,7 +1807,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1862,7 +1862,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1915,7 +1915,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -1968,7 +1968,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -2021,7 +2021,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2074,7 +2074,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2127,7 +2127,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2180,7 +2180,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2286,7 +2286,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2340,7 +2340,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2393,7 +2393,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2446,7 +2446,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2499,7 +2499,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2552,7 +2552,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2605,7 +2605,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2750,7 +2750,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -2767,7 +2767,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2803,7 +2803,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -2820,7 +2820,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2856,7 +2856,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -2873,7 +2873,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -2909,7 +2909,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -2926,7 +2926,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -2962,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -3250,7 +3250,7 @@
         <v>93</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3259,7 +3259,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3296,7 +3296,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -3310,7 +3310,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3347,7 +3347,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -3361,7 +3361,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3398,7 +3398,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -3412,7 +3412,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3449,7 +3449,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -3463,7 +3463,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3500,7 +3500,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -3514,7 +3514,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3551,7 +3551,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -3565,7 +3565,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3602,7 +3602,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
@@ -3616,7 +3616,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3653,7 +3653,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -3667,7 +3667,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3704,7 +3704,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
@@ -3718,7 +3718,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3755,7 +3755,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
@@ -3763,7 +3763,7 @@
         <v>94</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3772,7 +3772,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3808,7 +3808,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
@@ -3822,7 +3822,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3858,7 +3858,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -3872,7 +3872,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3908,7 +3908,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
@@ -3922,7 +3922,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3958,7 +3958,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
@@ -3972,7 +3972,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4008,7 +4008,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64">
@@ -4022,7 +4022,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4058,7 +4058,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -4072,7 +4072,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4108,7 +4108,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
@@ -4122,7 +4122,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4158,7 +4158,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67">
@@ -4172,7 +4172,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4208,7 +4208,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
@@ -4222,7 +4222,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4258,7 +4258,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69">
@@ -4266,7 +4266,7 @@
         <v>95</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4275,7 +4275,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4311,7 +4311,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
@@ -4325,7 +4325,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4361,7 +4361,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71">
@@ -4375,7 +4375,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4411,7 +4411,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72">
@@ -4425,7 +4425,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4461,7 +4461,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -4475,7 +4475,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4511,7 +4511,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
@@ -4525,7 +4525,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4561,7 +4561,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
@@ -4575,7 +4575,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4611,7 +4611,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76">
@@ -4625,7 +4625,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4661,7 +4661,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77">
@@ -4675,7 +4675,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4711,7 +4711,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="78">
@@ -4725,7 +4725,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4761,7 +4761,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79">
@@ -4769,7 +4769,7 @@
         <v>96</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -4778,7 +4778,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -4815,7 +4815,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80">
@@ -4829,7 +4829,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -4866,7 +4866,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81">
@@ -4880,7 +4880,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -4917,7 +4917,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82">
@@ -4931,7 +4931,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -4968,7 +4968,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83">
@@ -4982,7 +4982,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5019,7 +5019,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84">
@@ -5033,7 +5033,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5070,7 +5070,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85">
@@ -5084,7 +5084,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5121,7 +5121,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86">
@@ -5135,7 +5135,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5172,7 +5172,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87">
@@ -5186,7 +5186,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5223,7 +5223,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
@@ -5237,7 +5237,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5274,7 +5274,7 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89">
@@ -5282,7 +5282,7 @@
         <v>97</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>98</v>
@@ -5305,8 +5305,8 @@
       <c r="K89" s="1">
         <v>3.0</v>
       </c>
-      <c r="L89" s="1">
-        <v>31.0</v>
+      <c r="L89" s="3">
+        <v>39.0</v>
       </c>
       <c r="M89" s="1">
         <v>3.0</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="90">
       <c r="B90" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>99</v>
@@ -5360,8 +5360,8 @@
       <c r="K90" s="1">
         <v>3.0</v>
       </c>
-      <c r="L90" s="1">
-        <v>32.0</v>
+      <c r="L90" s="3">
+        <v>40.0</v>
       </c>
       <c r="M90" s="1">
         <v>3.0</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="91">
       <c r="B91" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>100</v>
@@ -5415,8 +5415,8 @@
       <c r="K91" s="1">
         <v>3.0</v>
       </c>
-      <c r="L91" s="1">
-        <v>31.0</v>
+      <c r="L91" s="3">
+        <v>39.0</v>
       </c>
       <c r="M91" s="1">
         <v>3.0</v>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="92">
       <c r="B92" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>101</v>
@@ -5470,8 +5470,8 @@
       <c r="K92" s="1">
         <v>3.0</v>
       </c>
-      <c r="L92" s="1">
-        <v>31.0</v>
+      <c r="L92" s="3">
+        <v>39.0</v>
       </c>
       <c r="M92" s="1">
         <v>3.0</v>
@@ -5501,7 +5501,7 @@
     </row>
     <row r="93">
       <c r="B93" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>102</v>
@@ -5524,8 +5524,8 @@
       <c r="K93" s="1">
         <v>3.0</v>
       </c>
-      <c r="L93" s="1">
-        <v>31.0</v>
+      <c r="L93" s="3">
+        <v>39.0</v>
       </c>
       <c r="M93" s="1">
         <v>3.0</v>
@@ -5555,7 +5555,7 @@
     </row>
     <row r="94">
       <c r="B94" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>103</v>
@@ -5578,8 +5578,8 @@
       <c r="K94" s="1">
         <v>3.0</v>
       </c>
-      <c r="L94" s="1">
-        <v>31.0</v>
+      <c r="L94" s="3">
+        <v>39.0</v>
       </c>
       <c r="M94" s="1">
         <v>3.0</v>
@@ -5609,7 +5609,7 @@
     </row>
     <row r="95">
       <c r="B95" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>104</v>
@@ -5632,8 +5632,8 @@
       <c r="K95" s="1">
         <v>3.0</v>
       </c>
-      <c r="L95" s="1">
-        <v>31.0</v>
+      <c r="L95" s="3">
+        <v>39.0</v>
       </c>
       <c r="M95" s="1">
         <v>3.0</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="96">
       <c r="B96" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>105</v>
@@ -5686,8 +5686,8 @@
       <c r="K96" s="1">
         <v>3.0</v>
       </c>
-      <c r="L96" s="1">
-        <v>31.0</v>
+      <c r="L96" s="3">
+        <v>39.0</v>
       </c>
       <c r="M96" s="1">
         <v>3.0</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="97">
       <c r="B97" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>106</v>
@@ -5740,8 +5740,8 @@
       <c r="K97" s="1">
         <v>3.0</v>
       </c>
-      <c r="L97" s="1">
-        <v>31.0</v>
+      <c r="L97" s="3">
+        <v>39.0</v>
       </c>
       <c r="M97" s="1">
         <v>3.0</v>
@@ -5771,7 +5771,7 @@
     </row>
     <row r="98">
       <c r="B98" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>65</v>
@@ -5827,7 +5827,7 @@
     </row>
     <row r="99">
       <c r="B99" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D99" s="3">
         <v>4.0</v>
@@ -5904,7 +5904,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -5920,10 +5920,10 @@
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -6945,82 +6945,82 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -7028,23 +7028,23 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -7052,7 +7052,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -7060,12 +7060,12 @@
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>47</v>
@@ -7097,7 +7097,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>52</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,36 +13,90 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="109">
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
+  </si>
+  <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
+    <t>Down Payment 2 %</t>
+  </si>
+  <si>
+    <t>DP2 Due (months)</t>
+  </si>
+  <si>
+    <t>Installments Count</t>
+  </si>
+  <si>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
+  </si>
+  <si>
+    <t>Delivery (months)</t>
+  </si>
+  <si>
+    <t>First Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance Basis</t>
+  </si>
   <si>
     <t>Setting</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
-    <t>Project</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Type</t>
+    <t/>
   </si>
   <si>
     <t>Company Name</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>BUA</t>
+    <t>YOUD</t>
   </si>
   <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
-    <t>Phase</t>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
     <t>Currency</t>
@@ -51,84 +105,39 @@
     <t>EGP</t>
   </si>
   <si>
-    <t>Plan</t>
+    <t>Original Price</t>
   </si>
   <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
-    <t>Down Payment 2 %</t>
-  </si>
-  <si>
-    <t>DP2 Due (months)</t>
-  </si>
-  <si>
-    <t>Installments Count</t>
-  </si>
-  <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>Maintenance %</t>
-  </si>
-  <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
     <t>Column</t>
   </si>
   <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Meaning / المعنى</t>
   </si>
   <si>
-    <t>Ending Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>Maintenance Basis</t>
-  </si>
-  <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
@@ -147,12 +156,6 @@
     <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
@@ -186,6 +189,9 @@
     <t>Selling price</t>
   </si>
   <si>
+    <t>Inactive</t>
+  </si>
+  <si>
     <t>10% DP &amp; 8 Years</t>
   </si>
   <si>
@@ -219,6 +225,9 @@
     <t>YOUD EL BAHR</t>
   </si>
   <si>
+    <t>Active</t>
+  </si>
+  <si>
     <t>RTM</t>
   </si>
   <si>
@@ -304,9 +313,6 @@
   </si>
   <si>
     <t>SUMMER</t>
-  </si>
-  <si>
-    <t>YOUD-TEST</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 10 Years</t>
@@ -633,75 +639,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -710,7 +719,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -748,15 +757,18 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
-        <v>37</v>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" s="1">
         <v>8.0</v>
@@ -765,7 +777,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -803,15 +815,18 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="s">
-        <v>37</v>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" s="1">
         <v>8.0</v>
@@ -820,7 +835,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -858,15 +873,18 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="s">
-        <v>37</v>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F5" s="1">
         <v>8.0</v>
@@ -875,7 +893,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -898,10 +916,10 @@
       <c r="O5" s="1">
         <v>10.0</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>18.0</v>
       </c>
       <c r="R5" s="1">
@@ -912,15 +930,18 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="s">
-        <v>37</v>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6" s="1">
         <v>8.0</v>
@@ -929,7 +950,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -952,10 +973,10 @@
       <c r="O6" s="1">
         <v>10.0</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>18.0</v>
       </c>
       <c r="R6" s="1">
@@ -966,15 +987,18 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="s">
-        <v>37</v>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F7" s="1">
         <v>8.0</v>
@@ -983,7 +1007,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1006,10 +1030,10 @@
       <c r="O7" s="1">
         <v>10.0</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <v>18.0</v>
       </c>
       <c r="R7" s="1">
@@ -1020,15 +1044,18 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="s">
-        <v>37</v>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F8" s="1">
         <v>8.0</v>
@@ -1037,7 +1064,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1060,10 +1087,10 @@
       <c r="O8" s="1">
         <v>10.0</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="2">
         <v>18.0</v>
       </c>
       <c r="R8" s="1">
@@ -1074,15 +1101,18 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="s">
-        <v>37</v>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1">
         <v>8.0</v>
@@ -1091,7 +1121,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1114,10 +1144,10 @@
       <c r="O9" s="1">
         <v>10.0</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <v>18.0</v>
       </c>
       <c r="R9" s="1">
@@ -1128,15 +1158,18 @@
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="s">
-        <v>37</v>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10" s="1">
         <v>8.0</v>
@@ -1145,7 +1178,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1168,10 +1201,10 @@
       <c r="O10" s="1">
         <v>10.0</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <v>18.0</v>
       </c>
       <c r="R10" s="1">
@@ -1182,18 +1215,21 @@
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="s">
-        <v>37</v>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F11" s="1">
         <v>0.0</v>
@@ -1202,7 +1238,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1228,28 +1264,31 @@
       <c r="P11" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q11" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="3">
+      <c r="Q11" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R11" s="2">
         <v>18.0</v>
       </c>
       <c r="S11" s="1">
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2">
         <v>4.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F12" s="1">
         <v>0.0</v>
@@ -1258,7 +1297,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1295,15 +1334,18 @@
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="s">
-        <v>67</v>
+      <c r="B13" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1312,7 +1354,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1350,15 +1392,18 @@
         <v>6.0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="s">
-        <v>67</v>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F14" s="1">
         <v>8.0</v>
@@ -1367,7 +1412,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1405,15 +1450,18 @@
         <v>6.0</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="s">
-        <v>67</v>
+      <c r="B15" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1">
         <v>8.0</v>
@@ -1422,7 +1470,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1460,15 +1508,18 @@
         <v>6.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="s">
-        <v>67</v>
+      <c r="B16" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F16" s="1">
         <v>8.0</v>
@@ -1477,7 +1528,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1515,15 +1566,18 @@
         <v>6.0</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="s">
-        <v>67</v>
+      <c r="B17" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F17" s="1">
         <v>8.0</v>
@@ -1532,7 +1586,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1570,15 +1624,18 @@
         <v>6.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="s">
-        <v>67</v>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F18" s="1">
         <v>8.0</v>
@@ -1587,7 +1644,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1625,15 +1682,18 @@
         <v>6.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="s">
-        <v>67</v>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
@@ -1642,7 +1702,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1680,15 +1740,18 @@
         <v>6.0</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="s">
-        <v>67</v>
+      <c r="B20" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F20" s="1">
         <v>8.0</v>
@@ -1697,7 +1760,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1735,15 +1798,18 @@
         <v>6.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="s">
-        <v>67</v>
+      <c r="B21" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F21" s="1">
         <v>8.0</v>
@@ -1752,7 +1818,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1790,15 +1856,18 @@
         <v>6.0</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="s">
-        <v>67</v>
+      <c r="B22" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F22" s="1">
         <v>0.0</v>
@@ -1807,7 +1876,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1845,15 +1914,18 @@
         <v>6.0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F23" s="1">
         <v>2.0</v>
@@ -1862,7 +1934,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1898,15 +1970,18 @@
         <v>3.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="F24" s="1">
         <v>3.0</v>
@@ -1915,24 +1990,24 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="3">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2">
         <v>15.0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="J24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="2">
         <v>12.0</v>
       </c>
       <c r="M24" s="1">
         <v>3.0</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="2">
         <v>3.0</v>
       </c>
       <c r="O24" s="1">
@@ -1951,15 +2026,18 @@
         <v>3.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E25" s="3" t="s">
         <v>71</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="F25" s="1">
         <v>4.0</v>
@@ -1968,24 +2046,24 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" s="3">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2">
         <v>20.0</v>
       </c>
-      <c r="J25" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="3">
+      <c r="J25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="2">
         <v>16.0</v>
       </c>
       <c r="M25" s="1">
         <v>3.0</v>
       </c>
-      <c r="N25" s="3">
+      <c r="N25" s="2">
         <v>3.0</v>
       </c>
       <c r="O25" s="1">
@@ -2004,15 +2082,18 @@
         <v>3.0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="F26" s="1">
         <v>5.0</v>
@@ -2021,24 +2102,24 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="3">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2">
         <v>25.0</v>
       </c>
-      <c r="J26" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="J26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="2">
         <v>20.0</v>
       </c>
       <c r="M26" s="1">
         <v>3.0</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="2">
         <v>3.0</v>
       </c>
       <c r="O26" s="1">
@@ -2057,15 +2138,18 @@
         <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="F27" s="1">
         <v>6.0</v>
@@ -2074,24 +2158,24 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I27" s="3">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2">
         <v>30.0</v>
       </c>
-      <c r="J27" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="J27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="2">
         <v>24.0</v>
       </c>
       <c r="M27" s="1">
         <v>3.0</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="2">
         <v>3.0</v>
       </c>
       <c r="O27" s="1">
@@ -2110,15 +2194,18 @@
         <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="F28" s="1">
         <v>7.0</v>
@@ -2127,24 +2214,24 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I28" s="3">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2">
         <v>35.0</v>
       </c>
-      <c r="J28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="3">
+      <c r="J28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="2">
         <v>28.0</v>
       </c>
       <c r="M28" s="1">
         <v>3.0</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28" s="2">
         <v>3.0</v>
       </c>
       <c r="O28" s="1">
@@ -2163,15 +2250,18 @@
         <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="F29" s="1">
         <v>8.0</v>
@@ -2180,24 +2270,24 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I29" s="3">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2">
         <v>40.0</v>
       </c>
-      <c r="J29" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="J29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="2">
         <v>32.0</v>
       </c>
       <c r="M29" s="1">
         <v>3.0</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="2">
         <v>3.0</v>
       </c>
       <c r="O29" s="1">
@@ -2216,15 +2306,18 @@
         <v>3.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F30" s="1">
         <v>0.0</v>
@@ -2233,7 +2326,7 @@
         <v>15.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I30" s="1">
         <v>100.0</v>
@@ -2269,443 +2362,470 @@
         <v>3.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="3">
+      <c r="B31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="2">
         <v>4.0</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="2">
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I31" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="3">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="2">
         <v>0.0</v>
       </c>
       <c r="L31" s="1">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="M31" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N31" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O31" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P31" s="3">
+      <c r="M31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P31" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q31" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R31" s="3">
+      <c r="Q31" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R31" s="2">
         <v>15.0</v>
       </c>
-      <c r="S31" s="3">
+      <c r="S31" s="2">
         <v>3.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="B32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P32" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R32" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P33" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R33" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O34" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P34" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R34" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P35" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R35" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="2">
+        <v>36.0</v>
+      </c>
+      <c r="M36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P36" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R36" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="M37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P37" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R37" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F32" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="F38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G38" s="2">
         <v>15.0</v>
       </c>
-      <c r="J32" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="H38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I38" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P38" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q32" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="Q38" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R38" s="2">
         <v>15.0</v>
       </c>
-      <c r="S32" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F33" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I33" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>24.0</v>
-      </c>
-      <c r="M33" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N33" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O33" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P33" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R33" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="S33" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I34" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="3">
-        <v>28.0</v>
-      </c>
-      <c r="M34" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N34" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O34" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P34" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R34" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="S34" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I35" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="3">
-        <v>32.0</v>
-      </c>
-      <c r="M35" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N35" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O35" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P35" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R35" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="S35" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="G36" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I36" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="3">
-        <v>36.0</v>
-      </c>
-      <c r="M36" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N36" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O36" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P36" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="Q36" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R36" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="S36" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F37" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G37" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L37" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="M37" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N37" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O37" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P37" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="Q37" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R37" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="S37" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I38" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P38" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="Q38" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R38" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="S38" s="3">
+      <c r="S38" s="2">
         <v>3.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F39" s="1">
         <v>0.0</v>
@@ -2714,7 +2834,7 @@
         <v>25.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I39" s="1">
         <v>100.0</v>
@@ -2750,15 +2870,18 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F40" s="1">
         <v>8.0</v>
@@ -2767,7 +2890,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2803,15 +2926,18 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F41" s="1">
         <v>7.0</v>
@@ -2820,7 +2946,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2831,7 +2957,7 @@
       <c r="K41" s="1">
         <v>3.0</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="2">
         <v>27.0</v>
       </c>
       <c r="M41" s="1">
@@ -2856,15 +2982,18 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F42" s="1">
         <v>6.0</v>
@@ -2873,7 +3002,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -2884,7 +3013,7 @@
       <c r="K42" s="1">
         <v>3.0</v>
       </c>
-      <c r="L42" s="3">
+      <c r="L42" s="2">
         <v>23.0</v>
       </c>
       <c r="M42" s="1">
@@ -2909,15 +3038,18 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F43" s="1">
         <v>5.0</v>
@@ -2926,7 +3058,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -2937,7 +3069,7 @@
       <c r="K43" s="1">
         <v>3.0</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="2">
         <v>19.0</v>
       </c>
       <c r="M43" s="1">
@@ -2962,18 +3094,21 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C44" s="4">
         <v>20000.0</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F44" s="1">
         <v>0.0</v>
@@ -2982,7 +3117,7 @@
         <v>25.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I44" s="1">
         <v>100.0</v>
@@ -3018,18 +3153,21 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C45" s="4">
         <v>20000.0</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F45" s="1">
         <v>8.0</v>
@@ -3038,7 +3176,7 @@
         <v>0.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I45" s="1">
         <v>5.0</v>
@@ -3074,18 +3212,21 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C46" s="4">
         <v>20000.0</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F46" s="1">
         <v>7.0</v>
@@ -3094,7 +3235,7 @@
         <v>3.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I46" s="1">
         <v>5.0</v>
@@ -3105,7 +3246,7 @@
       <c r="K46" s="1">
         <v>3.0</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="2">
         <v>27.0</v>
       </c>
       <c r="M46" s="1">
@@ -3130,18 +3271,21 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C47" s="4">
         <v>20000.0</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F47" s="1">
         <v>6.0</v>
@@ -3150,7 +3294,7 @@
         <v>6.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I47" s="1">
         <v>5.0</v>
@@ -3161,7 +3305,7 @@
       <c r="K47" s="1">
         <v>3.0</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="2">
         <v>23.0</v>
       </c>
       <c r="M47" s="1">
@@ -3186,18 +3330,21 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C48" s="4">
         <v>20000.0</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F48" s="1">
         <v>5.0</v>
@@ -3206,7 +3353,7 @@
         <v>9.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I48" s="1">
         <v>5.0</v>
@@ -3217,7 +3364,7 @@
       <c r="K48" s="1">
         <v>3.0</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="2">
         <v>19.0</v>
       </c>
       <c r="M48" s="1">
@@ -3242,15 +3389,18 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3259,7 +3409,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3296,12 +3446,15 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U49" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F50" s="1">
         <v>8.0</v>
@@ -3310,7 +3463,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3347,12 +3500,15 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="51">
       <c r="E51" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F51" s="1">
         <v>8.0</v>
@@ -3361,7 +3517,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3398,12 +3554,15 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U51" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="52">
       <c r="E52" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F52" s="1">
         <v>8.0</v>
@@ -3412,7 +3571,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3449,12 +3608,15 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="53">
       <c r="E53" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F53" s="1">
         <v>8.0</v>
@@ -3463,7 +3625,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3500,12 +3662,15 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U53" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="E54" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F54" s="1">
         <v>8.0</v>
@@ -3514,7 +3679,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3551,12 +3716,15 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U54" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55">
       <c r="E55" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F55" s="1">
         <v>8.0</v>
@@ -3565,7 +3733,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3602,12 +3770,15 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U55" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="56">
       <c r="E56" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F56" s="1">
         <v>8.0</v>
@@ -3616,7 +3787,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3653,12 +3824,15 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U56" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F57" s="1">
         <v>8.0</v>
@@ -3667,7 +3841,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3704,12 +3878,15 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U57" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F58" s="1">
         <v>0.0</v>
@@ -3718,7 +3895,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3755,15 +3932,18 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U58" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3772,7 +3952,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3808,12 +3988,15 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U59" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F60" s="1">
         <v>8.0</v>
@@ -3822,7 +4005,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3858,12 +4041,15 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="61">
       <c r="E61" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F61" s="1">
         <v>8.0</v>
@@ -3872,7 +4058,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3908,12 +4094,15 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="62">
       <c r="E62" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1">
         <v>8.0</v>
@@ -3922,7 +4111,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3958,12 +4147,15 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U62" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="63">
       <c r="E63" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F63" s="1">
         <v>8.0</v>
@@ -3972,7 +4164,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4008,12 +4200,15 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="64">
       <c r="E64" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F64" s="1">
         <v>8.0</v>
@@ -4022,7 +4217,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4058,12 +4253,15 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="65">
       <c r="E65" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F65" s="1">
         <v>8.0</v>
@@ -4072,7 +4270,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4108,12 +4306,15 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="66">
       <c r="E66" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F66" s="1">
         <v>8.0</v>
@@ -4122,7 +4323,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4158,12 +4359,15 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="67">
       <c r="E67" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F67" s="1">
         <v>8.0</v>
@@ -4172,7 +4376,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4208,12 +4412,15 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U67" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="68">
       <c r="E68" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F68" s="1">
         <v>0.0</v>
@@ -4222,7 +4429,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4258,15 +4465,18 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U68" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>95</v>
+      <c r="A69" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4275,7 +4485,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4298,25 +4508,28 @@
       <c r="O69" s="1">
         <v>10.0</v>
       </c>
-      <c r="P69" s="3">
+      <c r="P69" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q69" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R69" s="3">
+      <c r="Q69" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R69" s="2">
         <v>30.0</v>
       </c>
-      <c r="S69" s="3">
+      <c r="S69" s="2">
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U69" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="70">
       <c r="E70" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F70" s="1">
         <v>8.0</v>
@@ -4325,7 +4538,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4348,25 +4561,28 @@
       <c r="O70" s="1">
         <v>10.0</v>
       </c>
-      <c r="P70" s="3">
+      <c r="P70" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q70" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R70" s="3">
+      <c r="Q70" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R70" s="2">
         <v>30.0</v>
       </c>
-      <c r="S70" s="3">
+      <c r="S70" s="2">
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="71">
       <c r="E71" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F71" s="1">
         <v>8.0</v>
@@ -4375,7 +4591,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4398,25 +4614,28 @@
       <c r="O71" s="1">
         <v>10.0</v>
       </c>
-      <c r="P71" s="3">
+      <c r="P71" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q71" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R71" s="3">
+      <c r="Q71" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R71" s="2">
         <v>30.0</v>
       </c>
-      <c r="S71" s="3">
+      <c r="S71" s="2">
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="72">
       <c r="E72" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F72" s="1">
         <v>8.0</v>
@@ -4425,7 +4644,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4448,25 +4667,28 @@
       <c r="O72" s="1">
         <v>10.0</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q72" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R72" s="3">
+      <c r="Q72" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R72" s="2">
         <v>30.0</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="2">
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U72" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="73">
       <c r="E73" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F73" s="1">
         <v>8.0</v>
@@ -4475,7 +4697,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4498,25 +4720,28 @@
       <c r="O73" s="1">
         <v>10.0</v>
       </c>
-      <c r="P73" s="3">
+      <c r="P73" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q73" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R73" s="3">
+      <c r="Q73" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R73" s="2">
         <v>30.0</v>
       </c>
-      <c r="S73" s="3">
+      <c r="S73" s="2">
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U73" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="74">
       <c r="E74" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F74" s="1">
         <v>8.0</v>
@@ -4525,7 +4750,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4548,25 +4773,28 @@
       <c r="O74" s="1">
         <v>10.0</v>
       </c>
-      <c r="P74" s="3">
+      <c r="P74" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q74" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R74" s="3">
+      <c r="Q74" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R74" s="2">
         <v>30.0</v>
       </c>
-      <c r="S74" s="3">
+      <c r="S74" s="2">
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="75">
       <c r="E75" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F75" s="1">
         <v>8.0</v>
@@ -4575,7 +4803,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4598,25 +4826,28 @@
       <c r="O75" s="1">
         <v>10.0</v>
       </c>
-      <c r="P75" s="3">
+      <c r="P75" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q75" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R75" s="3">
+      <c r="Q75" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R75" s="2">
         <v>30.0</v>
       </c>
-      <c r="S75" s="3">
+      <c r="S75" s="2">
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="76">
       <c r="E76" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F76" s="1">
         <v>8.0</v>
@@ -4625,7 +4856,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4648,25 +4879,28 @@
       <c r="O76" s="1">
         <v>10.0</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q76" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R76" s="3">
+      <c r="Q76" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R76" s="2">
         <v>30.0</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="2">
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U76" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="77">
       <c r="E77" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F77" s="1">
         <v>8.0</v>
@@ -4675,7 +4909,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4698,25 +4932,28 @@
       <c r="O77" s="1">
         <v>10.0</v>
       </c>
-      <c r="P77" s="3">
+      <c r="P77" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q77" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R77" s="3">
+      <c r="Q77" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R77" s="2">
         <v>30.0</v>
       </c>
-      <c r="S77" s="3">
+      <c r="S77" s="2">
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="78">
       <c r="E78" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F78" s="1">
         <v>0.0</v>
@@ -4725,7 +4962,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4748,28 +4985,31 @@
       <c r="O78" s="1">
         <v>10.0</v>
       </c>
-      <c r="P78" s="3">
+      <c r="P78" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q78" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R78" s="3">
+      <c r="Q78" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R78" s="2">
         <v>30.0</v>
       </c>
-      <c r="S78" s="3">
+      <c r="S78" s="2">
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="s">
-        <v>96</v>
+      <c r="A79" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -4778,7 +5018,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -4815,12 +5055,15 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="80">
       <c r="E80" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F80" s="1">
         <v>8.0</v>
@@ -4829,7 +5072,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -4866,12 +5109,15 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81">
       <c r="E81" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F81" s="1">
         <v>8.0</v>
@@ -4880,7 +5126,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -4917,12 +5163,15 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U81" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="82">
       <c r="E82" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F82" s="1">
         <v>8.0</v>
@@ -4931,7 +5180,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -4968,12 +5217,15 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="83">
       <c r="E83" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F83" s="1">
         <v>8.0</v>
@@ -4982,7 +5234,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5019,12 +5271,15 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="84">
       <c r="E84" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F84" s="1">
         <v>8.0</v>
@@ -5033,7 +5288,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5070,12 +5325,15 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="85">
       <c r="E85" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F85" s="1">
         <v>8.0</v>
@@ -5084,7 +5342,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5121,12 +5379,15 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U85" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86">
       <c r="E86" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F86" s="1">
         <v>8.0</v>
@@ -5135,7 +5396,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5172,12 +5433,15 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="87">
       <c r="E87" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F87" s="1">
         <v>8.0</v>
@@ -5186,7 +5450,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5223,12 +5487,15 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U87" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="88">
       <c r="E88" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F88" s="1">
         <v>0.0</v>
@@ -5237,7 +5504,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5274,27 +5541,30 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
+      </c>
+      <c r="U88" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="A89" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F89" s="2">
         <v>10.0</v>
       </c>
       <c r="G89" s="1">
         <v>0.0</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I89" s="1">
         <v>5.0</v>
@@ -5305,7 +5575,7 @@
       <c r="K89" s="1">
         <v>3.0</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="2">
         <v>39.0</v>
       </c>
       <c r="M89" s="1">
@@ -5332,24 +5602,27 @@
         <v>6.0</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U89" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F90" s="3">
+      <c r="B90" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F90" s="2">
         <v>10.0</v>
       </c>
       <c r="G90" s="1">
         <v>10.0</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I90" s="1">
         <v>10.0</v>
@@ -5360,7 +5633,7 @@
       <c r="K90" s="1">
         <v>3.0</v>
       </c>
-      <c r="L90" s="3">
+      <c r="L90" s="2">
         <v>40.0</v>
       </c>
       <c r="M90" s="1">
@@ -5387,24 +5660,27 @@
         <v>6.0</v>
       </c>
       <c r="T90" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U90" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="B91" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F91" s="2">
         <v>10.0</v>
       </c>
       <c r="G91" s="1">
         <v>15.0</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I91" s="1">
         <v>7.5</v>
@@ -5415,7 +5691,7 @@
       <c r="K91" s="1">
         <v>3.0</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="2">
         <v>39.0</v>
       </c>
       <c r="M91" s="1">
@@ -5442,24 +5718,27 @@
         <v>6.0</v>
       </c>
       <c r="T91" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U91" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F92" s="3">
+      <c r="B92" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F92" s="2">
         <v>10.0</v>
       </c>
       <c r="G92" s="1">
         <v>20.0</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I92" s="1">
         <v>10.0</v>
@@ -5470,7 +5749,7 @@
       <c r="K92" s="1">
         <v>3.0</v>
       </c>
-      <c r="L92" s="3">
+      <c r="L92" s="2">
         <v>39.0</v>
       </c>
       <c r="M92" s="1">
@@ -5482,10 +5761,10 @@
       <c r="O92" s="1">
         <v>10.0</v>
       </c>
-      <c r="P92" s="3">
+      <c r="P92" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q92" s="3">
+      <c r="Q92" s="2">
         <v>18.0</v>
       </c>
       <c r="R92" s="1">
@@ -5496,24 +5775,27 @@
         <v>6.0</v>
       </c>
       <c r="T92" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U92" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F93" s="3">
+      <c r="B93" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F93" s="2">
         <v>10.0</v>
       </c>
       <c r="G93" s="1">
         <v>25.0</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I93" s="1">
         <v>12.5</v>
@@ -5524,7 +5806,7 @@
       <c r="K93" s="1">
         <v>3.0</v>
       </c>
-      <c r="L93" s="3">
+      <c r="L93" s="2">
         <v>39.0</v>
       </c>
       <c r="M93" s="1">
@@ -5536,10 +5818,10 @@
       <c r="O93" s="1">
         <v>10.0</v>
       </c>
-      <c r="P93" s="3">
+      <c r="P93" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q93" s="3">
+      <c r="Q93" s="2">
         <v>18.0</v>
       </c>
       <c r="R93" s="1">
@@ -5550,24 +5832,27 @@
         <v>6.0</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U93" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="B94" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F94" s="2">
         <v>10.0</v>
       </c>
       <c r="G94" s="1">
         <v>30.0</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I94" s="1">
         <v>15.0</v>
@@ -5578,7 +5863,7 @@
       <c r="K94" s="1">
         <v>3.0</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="2">
         <v>39.0</v>
       </c>
       <c r="M94" s="1">
@@ -5590,10 +5875,10 @@
       <c r="O94" s="1">
         <v>10.0</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="2">
         <v>18.0</v>
       </c>
       <c r="R94" s="1">
@@ -5604,24 +5889,27 @@
         <v>6.0</v>
       </c>
       <c r="T94" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U94" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F95" s="3">
+      <c r="B95" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F95" s="2">
         <v>10.0</v>
       </c>
       <c r="G95" s="1">
         <v>35.0</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I95" s="1">
         <v>17.5</v>
@@ -5632,7 +5920,7 @@
       <c r="K95" s="1">
         <v>3.0</v>
       </c>
-      <c r="L95" s="3">
+      <c r="L95" s="2">
         <v>39.0</v>
       </c>
       <c r="M95" s="1">
@@ -5644,10 +5932,10 @@
       <c r="O95" s="1">
         <v>10.0</v>
       </c>
-      <c r="P95" s="3">
+      <c r="P95" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q95" s="3">
+      <c r="Q95" s="2">
         <v>18.0</v>
       </c>
       <c r="R95" s="1">
@@ -5658,24 +5946,27 @@
         <v>6.0</v>
       </c>
       <c r="T95" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U95" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="B96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F96" s="2">
         <v>10.0</v>
       </c>
       <c r="G96" s="1">
         <v>40.0</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I96" s="1">
         <v>20.0</v>
@@ -5686,7 +5977,7 @@
       <c r="K96" s="1">
         <v>3.0</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="2">
         <v>39.0</v>
       </c>
       <c r="M96" s="1">
@@ -5698,10 +5989,10 @@
       <c r="O96" s="1">
         <v>10.0</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="2">
         <v>18.0</v>
       </c>
       <c r="R96" s="1">
@@ -5712,24 +6003,27 @@
         <v>6.0</v>
       </c>
       <c r="T96" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U96" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F97" s="3">
+      <c r="B97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F97" s="2">
         <v>10.0</v>
       </c>
       <c r="G97" s="1">
         <v>45.0</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I97" s="1">
         <v>22.5</v>
@@ -5740,7 +6034,7 @@
       <c r="K97" s="1">
         <v>3.0</v>
       </c>
-      <c r="L97" s="3">
+      <c r="L97" s="2">
         <v>39.0</v>
       </c>
       <c r="M97" s="1">
@@ -5752,10 +6046,10 @@
       <c r="O97" s="1">
         <v>10.0</v>
       </c>
-      <c r="P97" s="3">
+      <c r="P97" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q97" s="3">
+      <c r="Q97" s="2">
         <v>18.0</v>
       </c>
       <c r="R97" s="1">
@@ -5766,18 +6060,21 @@
         <v>6.0</v>
       </c>
       <c r="T97" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U97" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="3" t="s">
-        <v>37</v>
+      <c r="B98" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F98" s="1">
         <v>0.0</v>
@@ -5786,7 +6083,7 @@
         <v>50.0</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I98" s="1">
         <v>25.0</v>
@@ -5812,28 +6109,31 @@
       <c r="P98" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q98" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R98" s="3">
+      <c r="Q98" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R98" s="2">
         <v>18.0</v>
       </c>
       <c r="S98" s="1">
         <v>6.0</v>
       </c>
       <c r="T98" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U98" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D99" s="3">
+      <c r="B99" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D99" s="2">
         <v>4.0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F99" s="1">
         <v>0.0</v>
@@ -5842,7 +6142,7 @@
         <v>50.0</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I99" s="1">
         <v>25.0</v>
@@ -5879,7 +6179,10 @@
         <v>6.0</v>
       </c>
       <c r="T99" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="U99" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -5904,26 +6207,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -6945,186 +7248,186 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>15</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,20 +13,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="115">
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t/>
+  </si>
   <si>
     <t>Project</t>
   </si>
   <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
+  </si>
+  <si>
     <t>BUA</t>
   </si>
   <si>
     <t>Phase</t>
   </si>
   <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
     <t>Plan</t>
   </si>
   <si>
@@ -45,120 +75,90 @@
     <t>Down Payment 2 %</t>
   </si>
   <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
     <t>Installments Count</t>
   </si>
   <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
     <t>Installment Every (months)</t>
   </si>
   <si>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+  </si>
+  <si>
     <t>First Installment Due (months)</t>
   </si>
   <si>
     <t>Maintenance %</t>
   </si>
   <si>
+    <t>Column</t>
+  </si>
+  <si>
     <t>Delivery (months)</t>
   </si>
   <si>
+    <t>Meaning / المعنى</t>
+  </si>
+  <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+  </si>
+  <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
-    <t>Setting</t>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>How to fill the Projects sheet</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Company Name</t>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
+  </si>
+  <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
     <t>YOUD</t>
   </si>
   <si>
-    <t>Alahly Sabbour</t>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>EGP</t>
+    <t>Number of equal installments / عدد الأقساط</t>
+  </si>
+  <si>
+    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
     <t>Original Price</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
-  </si>
-  <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
-  </si>
-  <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
-  </si>
-  <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
-  </si>
-  <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
-  </si>
-  <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
-    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
-  </si>
-  <si>
     <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
   </si>
   <si>
@@ -315,6 +315,9 @@
     <t>SUMMER</t>
   </si>
   <si>
+    <t>Chalet</t>
+  </si>
+  <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 10 Years</t>
   </si>
   <si>
@@ -340,6 +343,21 @@
   </si>
   <si>
     <t>22.5% DP &amp; 22.5% After 3 Months &amp; 10 Years</t>
+  </si>
+  <si>
+    <t>VIllas</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 9 Years</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 7 Years</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 6 Years</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 5 Years</t>
   </si>
 </sst>
 </file>
@@ -639,78 +657,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -719,7 +737,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -759,13 +777,13 @@
       <c r="T2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="s">
-        <v>25</v>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -777,7 +795,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -817,13 +835,13 @@
       <c r="T3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="U3" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="s">
-        <v>25</v>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -835,7 +853,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -875,13 +893,13 @@
       <c r="T4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="U4" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="s">
-        <v>25</v>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -893,7 +911,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -916,10 +934,10 @@
       <c r="O5" s="1">
         <v>10.0</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="3">
         <v>18.0</v>
       </c>
       <c r="R5" s="1">
@@ -932,13 +950,13 @@
       <c r="T5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="U5" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="s">
-        <v>25</v>
+      <c r="B6" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -950,7 +968,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -973,10 +991,10 @@
       <c r="O6" s="1">
         <v>10.0</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="3">
         <v>18.0</v>
       </c>
       <c r="R6" s="1">
@@ -989,13 +1007,13 @@
       <c r="T6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="U6" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="s">
-        <v>25</v>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1007,7 +1025,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1030,10 +1048,10 @@
       <c r="O7" s="1">
         <v>10.0</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="3">
         <v>18.0</v>
       </c>
       <c r="R7" s="1">
@@ -1046,13 +1064,13 @@
       <c r="T7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="U7" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="s">
-        <v>25</v>
+      <c r="B8" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1064,7 +1082,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1087,10 +1105,10 @@
       <c r="O8" s="1">
         <v>10.0</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="3">
         <v>18.0</v>
       </c>
       <c r="R8" s="1">
@@ -1103,13 +1121,13 @@
       <c r="T8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="U8" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="s">
-        <v>25</v>
+      <c r="B9" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1121,7 +1139,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1144,10 +1162,10 @@
       <c r="O9" s="1">
         <v>10.0</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="3">
         <v>18.0</v>
       </c>
       <c r="R9" s="1">
@@ -1160,13 +1178,13 @@
       <c r="T9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="U9" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="s">
-        <v>25</v>
+      <c r="B10" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1178,7 +1196,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1201,10 +1219,10 @@
       <c r="O10" s="1">
         <v>10.0</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="3">
         <v>18.0</v>
       </c>
       <c r="R10" s="1">
@@ -1217,13 +1235,13 @@
       <c r="T10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="U10" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="s">
-        <v>25</v>
+      <c r="B11" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1238,7 +1256,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1264,10 +1282,10 @@
       <c r="P11" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q11" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="2">
+      <c r="Q11" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R11" s="3">
         <v>18.0</v>
       </c>
       <c r="S11" s="1">
@@ -1276,15 +1294,15 @@
       <c r="T11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="U11" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3">
         <v>4.0</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1297,7 +1315,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1336,16 +1354,16 @@
       <c r="T12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="U12" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1354,7 +1372,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1394,12 +1412,12 @@
       <c r="T13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="U13" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1412,7 +1430,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1452,12 +1470,12 @@
       <c r="T14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="U14" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1470,7 +1488,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1510,12 +1528,12 @@
       <c r="T15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="U15" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1528,7 +1546,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1568,12 +1586,12 @@
       <c r="T16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U16" s="2" t="s">
+      <c r="U16" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1586,7 +1604,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1626,12 +1644,12 @@
       <c r="T17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="U17" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1644,7 +1662,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1684,12 +1702,12 @@
       <c r="T18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U18" s="2" t="s">
+      <c r="U18" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1702,7 +1720,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1742,12 +1760,12 @@
       <c r="T19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U19" s="2" t="s">
+      <c r="U19" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1760,7 +1778,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1800,12 +1818,12 @@
       <c r="T20" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="U20" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1818,7 +1836,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1858,12 +1876,12 @@
       <c r="T21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="U21" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1876,7 +1894,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1916,7 +1934,7 @@
       <c r="T22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="U22" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1934,7 +1952,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1972,7 +1990,7 @@
       <c r="T23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="U23" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1980,7 +1998,7 @@
       <c r="B24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F24" s="1">
@@ -1990,24 +2008,24 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2">
+        <v>47</v>
+      </c>
+      <c r="I24" s="3">
         <v>15.0</v>
       </c>
-      <c r="J24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="2">
+      <c r="J24" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="3">
         <v>12.0</v>
       </c>
       <c r="M24" s="1">
         <v>3.0</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="3">
         <v>3.0</v>
       </c>
       <c r="O24" s="1">
@@ -2028,7 +2046,7 @@
       <c r="T24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U24" s="2" t="s">
+      <c r="U24" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2036,7 +2054,7 @@
       <c r="B25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F25" s="1">
@@ -2046,24 +2064,24 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2">
+        <v>47</v>
+      </c>
+      <c r="I25" s="3">
         <v>20.0</v>
       </c>
-      <c r="J25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="2">
+      <c r="J25" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="3">
         <v>16.0</v>
       </c>
       <c r="M25" s="1">
         <v>3.0</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="3">
         <v>3.0</v>
       </c>
       <c r="O25" s="1">
@@ -2084,7 +2102,7 @@
       <c r="T25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U25" s="2" t="s">
+      <c r="U25" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2092,7 +2110,7 @@
       <c r="B26" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F26" s="1">
@@ -2102,24 +2120,24 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2">
+        <v>47</v>
+      </c>
+      <c r="I26" s="3">
         <v>25.0</v>
       </c>
-      <c r="J26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="2">
+      <c r="J26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="3">
         <v>20.0</v>
       </c>
       <c r="M26" s="1">
         <v>3.0</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="3">
         <v>3.0</v>
       </c>
       <c r="O26" s="1">
@@ -2140,7 +2158,7 @@
       <c r="T26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U26" s="2" t="s">
+      <c r="U26" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2148,7 +2166,7 @@
       <c r="B27" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>76</v>
       </c>
       <c r="F27" s="1">
@@ -2158,24 +2176,24 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2">
+        <v>47</v>
+      </c>
+      <c r="I27" s="3">
         <v>30.0</v>
       </c>
-      <c r="J27" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="2">
+      <c r="J27" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="3">
         <v>24.0</v>
       </c>
       <c r="M27" s="1">
         <v>3.0</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N27" s="3">
         <v>3.0</v>
       </c>
       <c r="O27" s="1">
@@ -2196,7 +2214,7 @@
       <c r="T27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="U27" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2204,7 +2222,7 @@
       <c r="B28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>77</v>
       </c>
       <c r="F28" s="1">
@@ -2214,24 +2232,24 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2">
+        <v>47</v>
+      </c>
+      <c r="I28" s="3">
         <v>35.0</v>
       </c>
-      <c r="J28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="2">
+      <c r="J28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="3">
         <v>28.0</v>
       </c>
       <c r="M28" s="1">
         <v>3.0</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" s="3">
         <v>3.0</v>
       </c>
       <c r="O28" s="1">
@@ -2252,7 +2270,7 @@
       <c r="T28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U28" s="2" t="s">
+      <c r="U28" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2260,7 +2278,7 @@
       <c r="B29" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>78</v>
       </c>
       <c r="F29" s="1">
@@ -2270,24 +2288,24 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2">
+        <v>47</v>
+      </c>
+      <c r="I29" s="3">
         <v>40.0</v>
       </c>
-      <c r="J29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="2">
+      <c r="J29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="3">
         <v>32.0</v>
       </c>
       <c r="M29" s="1">
         <v>3.0</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N29" s="3">
         <v>3.0</v>
       </c>
       <c r="O29" s="1">
@@ -2308,7 +2326,7 @@
       <c r="T29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="U29" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2364,456 +2382,456 @@
       <c r="T30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U30" s="2" t="s">
+      <c r="U30" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>4.0</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="2">
+        <v>47</v>
+      </c>
+      <c r="I31" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="3">
         <v>0.0</v>
       </c>
       <c r="L31" s="1">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="M31" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N31" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O31" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P31" s="2">
+      <c r="M31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P31" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q31" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R31" s="2">
+      <c r="Q31" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R31" s="3">
         <v>15.0</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31" s="3">
         <v>3.0</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U31" s="2" t="s">
+      <c r="U31" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>5.0</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="3">
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2">
+        <v>47</v>
+      </c>
+      <c r="I32" s="3">
         <v>15.0</v>
       </c>
-      <c r="J32" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="2">
+      <c r="J32" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="3">
         <v>20.0</v>
       </c>
-      <c r="M32" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N32" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P32" s="2">
+      <c r="M32" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P32" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q32" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R32" s="2">
+      <c r="Q32" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R32" s="3">
         <v>15.0</v>
       </c>
-      <c r="S32" s="2">
+      <c r="S32" s="3">
         <v>3.0</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U32" s="2" t="s">
+      <c r="U32" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F33" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="G33" s="2">
+      <c r="F33" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="G33" s="3">
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2">
+        <v>47</v>
+      </c>
+      <c r="I33" s="3">
         <v>20.0</v>
       </c>
-      <c r="J33" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="2">
+      <c r="J33" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="3">
         <v>24.0</v>
       </c>
-      <c r="M33" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N33" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O33" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P33" s="2">
+      <c r="M33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P33" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q33" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R33" s="2">
+      <c r="Q33" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R33" s="3">
         <v>15.0</v>
       </c>
-      <c r="S33" s="2">
+      <c r="S33" s="3">
         <v>3.0</v>
       </c>
       <c r="T33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="U33" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>7.0</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="3">
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2">
+        <v>47</v>
+      </c>
+      <c r="I34" s="3">
         <v>25.0</v>
       </c>
-      <c r="J34" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="2">
+      <c r="J34" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="3">
         <v>28.0</v>
       </c>
-      <c r="M34" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N34" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O34" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="M34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P34" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q34" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R34" s="2">
+      <c r="Q34" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R34" s="3">
         <v>15.0</v>
       </c>
-      <c r="S34" s="2">
+      <c r="S34" s="3">
         <v>3.0</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U34" s="2" t="s">
+      <c r="U34" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>8.0</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="3">
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2">
+        <v>47</v>
+      </c>
+      <c r="I35" s="3">
         <v>30.0</v>
       </c>
-      <c r="J35" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="2">
+      <c r="J35" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="3">
         <v>32.0</v>
       </c>
-      <c r="M35" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N35" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P35" s="2">
+      <c r="M35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P35" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q35" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R35" s="2">
+      <c r="Q35" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R35" s="3">
         <v>15.0</v>
       </c>
-      <c r="S35" s="2">
+      <c r="S35" s="3">
         <v>3.0</v>
       </c>
       <c r="T35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U35" s="2" t="s">
+      <c r="U35" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>9.0</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2">
+        <v>47</v>
+      </c>
+      <c r="I36" s="3">
         <v>35.0</v>
       </c>
-      <c r="J36" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="2">
+      <c r="J36" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="3">
         <v>36.0</v>
       </c>
-      <c r="M36" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N36" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O36" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P36" s="2">
+      <c r="M36" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O36" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P36" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q36" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R36" s="2">
+      <c r="Q36" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R36" s="3">
         <v>15.0</v>
       </c>
-      <c r="S36" s="2">
+      <c r="S36" s="3">
         <v>3.0</v>
       </c>
       <c r="T36" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U36" s="2" t="s">
+      <c r="U36" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F37" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="G37" s="2">
+      <c r="F37" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G37" s="3">
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2">
+        <v>47</v>
+      </c>
+      <c r="I37" s="3">
         <v>40.0</v>
       </c>
-      <c r="J37" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K37" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L37" s="2">
+      <c r="J37" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="3">
         <v>40.0</v>
       </c>
-      <c r="M37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O37" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P37" s="2">
+      <c r="M37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O37" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P37" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q37" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R37" s="2">
+      <c r="Q37" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R37" s="3">
         <v>15.0</v>
       </c>
-      <c r="S37" s="2">
+      <c r="S37" s="3">
         <v>3.0</v>
       </c>
       <c r="T37" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U37" s="2" t="s">
+      <c r="U37" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>80</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="F38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G38" s="3">
         <v>15.0</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="3">
         <v>100.0</v>
       </c>
-      <c r="J38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="J38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P38" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q38" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R38" s="2">
+      <c r="Q38" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R38" s="3">
         <v>15.0</v>
       </c>
-      <c r="S38" s="2">
+      <c r="S38" s="3">
         <v>3.0</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U38" s="2" t="s">
+      <c r="U38" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2870,9 +2888,9 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U39" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2890,7 +2908,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2926,9 +2944,9 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U40" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2946,7 +2964,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2957,7 +2975,7 @@
       <c r="K41" s="1">
         <v>3.0</v>
       </c>
-      <c r="L41" s="2">
+      <c r="L41" s="3">
         <v>27.0</v>
       </c>
       <c r="M41" s="1">
@@ -2982,9 +3000,9 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U41" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3002,7 +3020,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3013,7 +3031,7 @@
       <c r="K42" s="1">
         <v>3.0</v>
       </c>
-      <c r="L42" s="2">
+      <c r="L42" s="3">
         <v>23.0</v>
       </c>
       <c r="M42" s="1">
@@ -3038,9 +3056,9 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3058,7 +3076,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3069,7 +3087,7 @@
       <c r="K43" s="1">
         <v>3.0</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L43" s="3">
         <v>19.0</v>
       </c>
       <c r="M43" s="1">
@@ -3094,9 +3112,9 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3155,7 +3173,7 @@
       <c r="T44" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U44" s="2" t="s">
+      <c r="U44" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3214,7 +3232,7 @@
       <c r="T45" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U45" s="2" t="s">
+      <c r="U45" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3246,7 +3264,7 @@
       <c r="K46" s="1">
         <v>3.0</v>
       </c>
-      <c r="L46" s="2">
+      <c r="L46" s="3">
         <v>27.0</v>
       </c>
       <c r="M46" s="1">
@@ -3273,7 +3291,7 @@
       <c r="T46" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U46" s="2" t="s">
+      <c r="U46" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3305,7 +3323,7 @@
       <c r="K47" s="1">
         <v>3.0</v>
       </c>
-      <c r="L47" s="2">
+      <c r="L47" s="3">
         <v>23.0</v>
       </c>
       <c r="M47" s="1">
@@ -3332,7 +3350,7 @@
       <c r="T47" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U47" s="2" t="s">
+      <c r="U47" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3364,7 +3382,7 @@
       <c r="K48" s="1">
         <v>3.0</v>
       </c>
-      <c r="L48" s="2">
+      <c r="L48" s="3">
         <v>19.0</v>
       </c>
       <c r="M48" s="1">
@@ -3391,7 +3409,7 @@
       <c r="T48" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U48" s="2" t="s">
+      <c r="U48" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3400,7 +3418,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3409,7 +3427,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3446,9 +3464,9 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3463,7 +3481,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3500,9 +3518,9 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3517,7 +3535,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3554,9 +3572,9 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3571,7 +3589,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3608,9 +3626,9 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U52" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3625,7 +3643,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3662,9 +3680,9 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U53" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3679,7 +3697,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3716,9 +3734,9 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U54" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3733,7 +3751,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3770,9 +3788,9 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U55" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3787,7 +3805,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3824,9 +3842,9 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U56" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U56" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3841,7 +3859,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3878,9 +3896,9 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U57" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3895,7 +3913,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3932,9 +3950,9 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U58" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U58" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3943,7 +3961,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3952,7 +3970,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3988,9 +4006,9 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U59" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U59" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4005,7 +4023,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4041,9 +4059,9 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U60" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U60" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4058,7 +4076,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4094,9 +4112,9 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U61" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U61" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4111,7 +4129,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4147,9 +4165,9 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U62" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U62" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4164,7 +4182,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4200,9 +4218,9 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U63" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U63" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4217,7 +4235,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4253,9 +4271,9 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U64" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U64" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4270,7 +4288,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4306,9 +4324,9 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U65" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U65" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4323,7 +4341,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4359,9 +4377,9 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U66" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U66" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4376,7 +4394,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4412,9 +4430,9 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U67" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U67" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4429,7 +4447,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4465,18 +4483,18 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U68" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U68" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4485,7 +4503,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4508,22 +4526,22 @@
       <c r="O69" s="1">
         <v>10.0</v>
       </c>
-      <c r="P69" s="2">
+      <c r="P69" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q69" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R69" s="2">
+      <c r="Q69" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R69" s="3">
         <v>30.0</v>
       </c>
-      <c r="S69" s="2">
+      <c r="S69" s="3">
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U69" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U69" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4538,7 +4556,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4561,22 +4579,22 @@
       <c r="O70" s="1">
         <v>10.0</v>
       </c>
-      <c r="P70" s="2">
+      <c r="P70" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q70" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R70" s="2">
+      <c r="Q70" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R70" s="3">
         <v>30.0</v>
       </c>
-      <c r="S70" s="2">
+      <c r="S70" s="3">
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U70" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U70" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4591,7 +4609,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4614,22 +4632,22 @@
       <c r="O71" s="1">
         <v>10.0</v>
       </c>
-      <c r="P71" s="2">
+      <c r="P71" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q71" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R71" s="2">
+      <c r="Q71" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R71" s="3">
         <v>30.0</v>
       </c>
-      <c r="S71" s="2">
+      <c r="S71" s="3">
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U71" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U71" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4644,7 +4662,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4667,22 +4685,22 @@
       <c r="O72" s="1">
         <v>10.0</v>
       </c>
-      <c r="P72" s="2">
+      <c r="P72" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q72" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R72" s="2">
+      <c r="Q72" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R72" s="3">
         <v>30.0</v>
       </c>
-      <c r="S72" s="2">
+      <c r="S72" s="3">
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U72" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U72" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4697,7 +4715,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4720,22 +4738,22 @@
       <c r="O73" s="1">
         <v>10.0</v>
       </c>
-      <c r="P73" s="2">
+      <c r="P73" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q73" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R73" s="2">
+      <c r="Q73" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R73" s="3">
         <v>30.0</v>
       </c>
-      <c r="S73" s="2">
+      <c r="S73" s="3">
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U73" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U73" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4750,7 +4768,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4773,22 +4791,22 @@
       <c r="O74" s="1">
         <v>10.0</v>
       </c>
-      <c r="P74" s="2">
+      <c r="P74" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q74" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R74" s="2">
+      <c r="Q74" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R74" s="3">
         <v>30.0</v>
       </c>
-      <c r="S74" s="2">
+      <c r="S74" s="3">
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U74" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U74" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4803,7 +4821,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4826,22 +4844,22 @@
       <c r="O75" s="1">
         <v>10.0</v>
       </c>
-      <c r="P75" s="2">
+      <c r="P75" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q75" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R75" s="2">
+      <c r="Q75" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R75" s="3">
         <v>30.0</v>
       </c>
-      <c r="S75" s="2">
+      <c r="S75" s="3">
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U75" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U75" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4856,7 +4874,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4879,22 +4897,22 @@
       <c r="O76" s="1">
         <v>10.0</v>
       </c>
-      <c r="P76" s="2">
+      <c r="P76" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q76" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R76" s="2">
+      <c r="Q76" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R76" s="3">
         <v>30.0</v>
       </c>
-      <c r="S76" s="2">
+      <c r="S76" s="3">
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U76" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U76" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4909,7 +4927,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4932,22 +4950,22 @@
       <c r="O77" s="1">
         <v>10.0</v>
       </c>
-      <c r="P77" s="2">
+      <c r="P77" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q77" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R77" s="2">
+      <c r="Q77" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R77" s="3">
         <v>30.0</v>
       </c>
-      <c r="S77" s="2">
+      <c r="S77" s="3">
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U77" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U77" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4962,7 +4980,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4985,31 +5003,31 @@
       <c r="O78" s="1">
         <v>10.0</v>
       </c>
-      <c r="P78" s="2">
+      <c r="P78" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q78" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R78" s="2">
+      <c r="Q78" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R78" s="3">
         <v>30.0</v>
       </c>
-      <c r="S78" s="2">
+      <c r="S78" s="3">
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U78" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U78" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="3" t="s">
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5018,7 +5036,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5055,9 +5073,9 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U79" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U79" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5072,7 +5090,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5109,9 +5127,9 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U80" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U80" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5126,7 +5144,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5163,9 +5181,9 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U81" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U81" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5180,7 +5198,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5217,9 +5235,9 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U82" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U82" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5234,7 +5252,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5271,9 +5289,9 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U83" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U83" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5288,7 +5306,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5325,9 +5343,9 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U84" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U84" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5342,7 +5360,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5379,9 +5397,9 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U85" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U85" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5396,7 +5414,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5433,9 +5451,9 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U86" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U86" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5450,7 +5468,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5487,9 +5505,9 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U87" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U87" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5504,7 +5522,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5541,23 +5559,23 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U88" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U88" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E89" s="2" t="s">
+      <c r="A89" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F89" s="2">
+      <c r="E89" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F89" s="3">
         <v>10.0</v>
       </c>
       <c r="G89" s="1">
@@ -5575,7 +5593,7 @@
       <c r="K89" s="1">
         <v>3.0</v>
       </c>
-      <c r="L89" s="2">
+      <c r="L89" s="3">
         <v>39.0</v>
       </c>
       <c r="M89" s="1">
@@ -5604,18 +5622,18 @@
       <c r="T89" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U89" s="2" t="s">
+      <c r="U89" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F90" s="2">
+      <c r="B90" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F90" s="3">
         <v>10.0</v>
       </c>
       <c r="G90" s="1">
@@ -5633,7 +5651,7 @@
       <c r="K90" s="1">
         <v>3.0</v>
       </c>
-      <c r="L90" s="2">
+      <c r="L90" s="3">
         <v>40.0</v>
       </c>
       <c r="M90" s="1">
@@ -5662,18 +5680,18 @@
       <c r="T90" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U90" s="2" t="s">
+      <c r="U90" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F91" s="2">
+      <c r="B91" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F91" s="3">
         <v>10.0</v>
       </c>
       <c r="G91" s="1">
@@ -5691,7 +5709,7 @@
       <c r="K91" s="1">
         <v>3.0</v>
       </c>
-      <c r="L91" s="2">
+      <c r="L91" s="3">
         <v>39.0</v>
       </c>
       <c r="M91" s="1">
@@ -5720,18 +5738,18 @@
       <c r="T91" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U91" s="2" t="s">
+      <c r="U91" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F92" s="2">
+      <c r="B92" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F92" s="3">
         <v>10.0</v>
       </c>
       <c r="G92" s="1">
@@ -5749,7 +5767,7 @@
       <c r="K92" s="1">
         <v>3.0</v>
       </c>
-      <c r="L92" s="2">
+      <c r="L92" s="3">
         <v>39.0</v>
       </c>
       <c r="M92" s="1">
@@ -5761,10 +5779,10 @@
       <c r="O92" s="1">
         <v>10.0</v>
       </c>
-      <c r="P92" s="2">
+      <c r="P92" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q92" s="2">
+      <c r="Q92" s="3">
         <v>18.0</v>
       </c>
       <c r="R92" s="1">
@@ -5777,18 +5795,18 @@
       <c r="T92" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U92" s="2" t="s">
+      <c r="U92" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F93" s="2">
+      <c r="B93" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F93" s="3">
         <v>10.0</v>
       </c>
       <c r="G93" s="1">
@@ -5806,7 +5824,7 @@
       <c r="K93" s="1">
         <v>3.0</v>
       </c>
-      <c r="L93" s="2">
+      <c r="L93" s="3">
         <v>39.0</v>
       </c>
       <c r="M93" s="1">
@@ -5818,10 +5836,10 @@
       <c r="O93" s="1">
         <v>10.0</v>
       </c>
-      <c r="P93" s="2">
+      <c r="P93" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q93" s="2">
+      <c r="Q93" s="3">
         <v>18.0</v>
       </c>
       <c r="R93" s="1">
@@ -5834,18 +5852,18 @@
       <c r="T93" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U93" s="2" t="s">
+      <c r="U93" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F94" s="2">
+      <c r="B94" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F94" s="3">
         <v>10.0</v>
       </c>
       <c r="G94" s="1">
@@ -5863,7 +5881,7 @@
       <c r="K94" s="1">
         <v>3.0</v>
       </c>
-      <c r="L94" s="2">
+      <c r="L94" s="3">
         <v>39.0</v>
       </c>
       <c r="M94" s="1">
@@ -5875,10 +5893,10 @@
       <c r="O94" s="1">
         <v>10.0</v>
       </c>
-      <c r="P94" s="2">
+      <c r="P94" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q94" s="2">
+      <c r="Q94" s="3">
         <v>18.0</v>
       </c>
       <c r="R94" s="1">
@@ -5891,18 +5909,18 @@
       <c r="T94" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U94" s="2" t="s">
+      <c r="U94" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F95" s="2">
+      <c r="B95" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F95" s="3">
         <v>10.0</v>
       </c>
       <c r="G95" s="1">
@@ -5920,7 +5938,7 @@
       <c r="K95" s="1">
         <v>3.0</v>
       </c>
-      <c r="L95" s="2">
+      <c r="L95" s="3">
         <v>39.0</v>
       </c>
       <c r="M95" s="1">
@@ -5932,10 +5950,10 @@
       <c r="O95" s="1">
         <v>10.0</v>
       </c>
-      <c r="P95" s="2">
+      <c r="P95" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q95" s="2">
+      <c r="Q95" s="3">
         <v>18.0</v>
       </c>
       <c r="R95" s="1">
@@ -5948,18 +5966,18 @@
       <c r="T95" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U95" s="2" t="s">
+      <c r="U95" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F96" s="2">
+      <c r="B96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F96" s="3">
         <v>10.0</v>
       </c>
       <c r="G96" s="1">
@@ -5977,7 +5995,7 @@
       <c r="K96" s="1">
         <v>3.0</v>
       </c>
-      <c r="L96" s="2">
+      <c r="L96" s="3">
         <v>39.0</v>
       </c>
       <c r="M96" s="1">
@@ -5989,10 +6007,10 @@
       <c r="O96" s="1">
         <v>10.0</v>
       </c>
-      <c r="P96" s="2">
+      <c r="P96" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q96" s="2">
+      <c r="Q96" s="3">
         <v>18.0</v>
       </c>
       <c r="R96" s="1">
@@ -6005,18 +6023,18 @@
       <c r="T96" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U96" s="2" t="s">
+      <c r="U96" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F97" s="2">
+      <c r="B97" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F97" s="3">
         <v>10.0</v>
       </c>
       <c r="G97" s="1">
@@ -6034,7 +6052,7 @@
       <c r="K97" s="1">
         <v>3.0</v>
       </c>
-      <c r="L97" s="2">
+      <c r="L97" s="3">
         <v>39.0</v>
       </c>
       <c r="M97" s="1">
@@ -6046,10 +6064,10 @@
       <c r="O97" s="1">
         <v>10.0</v>
       </c>
-      <c r="P97" s="2">
+      <c r="P97" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q97" s="2">
+      <c r="Q97" s="3">
         <v>18.0</v>
       </c>
       <c r="R97" s="1">
@@ -6062,13 +6080,13 @@
       <c r="T97" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U97" s="2" t="s">
+      <c r="U97" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="2" t="s">
-        <v>25</v>
+      <c r="B98" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>67</v>
@@ -6109,10 +6127,10 @@
       <c r="P98" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q98" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R98" s="2">
+      <c r="Q98" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R98" s="3">
         <v>18.0</v>
       </c>
       <c r="S98" s="1">
@@ -6121,15 +6139,15 @@
       <c r="T98" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U98" s="2" t="s">
+      <c r="U98" s="3" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D99" s="2">
+      <c r="B99" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" s="3">
         <v>4.0</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -6181,7 +6199,343 @@
       <c r="T99" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U99" s="2" t="s">
+      <c r="U99" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F100" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I100" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>39.0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O100" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="S100" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F101" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I101" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="M101" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O101" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="S101" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F102" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>14.0</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I102" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>31.0</v>
+      </c>
+      <c r="M102" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O102" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="R102" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="S102" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T102" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F103" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="G103" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J103" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K103" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L103" s="3">
+        <v>27.0</v>
+      </c>
+      <c r="M103" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N103" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O103" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P103" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="Q103" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="R103" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="S103" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T103" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U103" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F104" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="G104" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I104" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J104" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K104" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L104" s="3">
+        <v>23.0</v>
+      </c>
+      <c r="M104" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N104" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O104" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P104" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="Q104" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="R104" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="S104" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T104" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U104" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F105" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G105" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I105" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J105" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K105" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L105" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="M105" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N105" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O105" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P105" s="3">
+        <v>48.0</v>
+      </c>
+      <c r="Q105" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="R105" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="S105" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T105" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U105" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6207,26 +6561,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -7248,135 +7602,135 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>48</v>
@@ -7400,7 +7754,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>53</v>
@@ -7408,25 +7762,25 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
     </row>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,30 +13,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="121">
+  <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
   <si>
     <t>Setting</t>
   </si>
   <si>
-    <t>How to fill the Projects sheet</t>
+    <t/>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Project</t>
+    <t>Type</t>
   </si>
   <si>
     <t>Company Name</t>
   </si>
   <si>
+    <t>BUA</t>
+  </si>
+  <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
-    <t>Type</t>
+    <t>Phase</t>
   </si>
   <si>
     <t>Currency</t>
@@ -45,90 +51,93 @@
     <t>EGP</t>
   </si>
   <si>
+    <t>Plan</t>
+  </si>
+  <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t>Phase</t>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
+  </si>
+  <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
+    <t>Down Payment 2 %</t>
+  </si>
+  <si>
+    <t>DP2 Due (months)</t>
   </si>
   <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Plan</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
-    <t>Down Payment 2 %</t>
+    <t>Installments Count</t>
+  </si>
+  <si>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
+  </si>
+  <si>
+    <t>Delivery (months)</t>
+  </si>
+  <si>
+    <t>First Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance Basis</t>
   </si>
   <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
-    <t>DP2 Due (months)</t>
+    <t>Status</t>
   </si>
   <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
-    <t>Installments Count</t>
-  </si>
-  <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
-    <t>Maintenance %</t>
+    <t>YOUD</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
     <t>Column</t>
   </si>
   <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
     <t>Meaning / المعنى</t>
   </si>
   <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
-    <t>Ending Installment Maintenance Due (months)</t>
+    <t>Original Price</t>
   </si>
   <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>Maintenance Basis</t>
-  </si>
-  <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
@@ -141,24 +150,15 @@
     <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
     <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
   </si>
   <si>
@@ -358,6 +358,24 @@
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 5 Years</t>
+  </si>
+  <si>
+    <t>10% &amp; 5% &amp; 8 years</t>
+  </si>
+  <si>
+    <t>10% &amp; 10% &amp; 9 years</t>
+  </si>
+  <si>
+    <t>15% &amp; 10% &amp; 10 years</t>
+  </si>
+  <si>
+    <t>The Mornings (Residental)</t>
+  </si>
+  <si>
+    <t>10% &amp; 5% &amp; 9 years</t>
+  </si>
+  <si>
+    <t>10% &amp; 10% &amp; 10 years</t>
   </si>
 </sst>
 </file>
@@ -657,78 +675,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -737,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -783,7 +801,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -795,7 +813,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -841,7 +859,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -853,7 +871,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -899,7 +917,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -911,7 +929,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -956,7 +974,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -968,7 +986,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -1013,7 +1031,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1025,7 +1043,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1070,7 +1088,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1082,7 +1100,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1127,7 +1145,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1139,7 +1157,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1184,7 +1202,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1196,7 +1214,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1241,7 +1259,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1256,7 +1274,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1300,7 +1318,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1315,7 +1333,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1363,7 +1381,7 @@
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1372,7 +1390,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1430,7 +1448,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1488,7 +1506,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1546,7 +1564,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1604,7 +1622,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1662,7 +1680,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1720,7 +1738,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1778,7 +1796,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1836,7 +1854,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1894,7 +1912,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1952,7 +1970,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -2008,7 +2026,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -2064,7 +2082,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -2120,7 +2138,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2176,7 +2194,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2232,7 +2250,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2288,7 +2306,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2400,7 +2418,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2457,7 +2475,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2513,7 +2531,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2569,7 +2587,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2625,7 +2643,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2681,7 +2699,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2737,7 +2755,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2888,7 +2906,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U39" s="3" t="s">
         <v>58</v>
@@ -2908,7 +2926,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2944,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>58</v>
@@ -2964,7 +2982,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -3000,7 +3018,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>58</v>
@@ -3020,7 +3038,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3056,7 +3074,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>58</v>
@@ -3076,7 +3094,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3112,7 +3130,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>58</v>
@@ -3418,7 +3436,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3427,7 +3445,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3464,7 +3482,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>70</v>
@@ -3481,7 +3499,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3518,7 +3536,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>70</v>
@@ -3535,7 +3553,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3572,7 +3590,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>70</v>
@@ -3589,7 +3607,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3626,7 +3644,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>70</v>
@@ -3643,7 +3661,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3680,7 +3698,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U53" s="3" t="s">
         <v>70</v>
@@ -3697,7 +3715,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3734,7 +3752,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>70</v>
@@ -3751,7 +3769,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3788,7 +3806,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U55" s="3" t="s">
         <v>70</v>
@@ -3805,7 +3823,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3842,7 +3860,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U56" s="3" t="s">
         <v>70</v>
@@ -3859,7 +3877,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3896,7 +3914,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>70</v>
@@ -3913,7 +3931,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3950,7 +3968,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>70</v>
@@ -3961,7 +3979,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3970,7 +3988,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -4006,7 +4024,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>70</v>
@@ -4023,7 +4041,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4059,7 +4077,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>70</v>
@@ -4076,7 +4094,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4112,7 +4130,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>70</v>
@@ -4129,7 +4147,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4165,7 +4183,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>70</v>
@@ -4182,7 +4200,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4218,7 +4236,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U63" s="3" t="s">
         <v>70</v>
@@ -4235,7 +4253,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4271,7 +4289,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U64" s="3" t="s">
         <v>70</v>
@@ -4288,7 +4306,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4324,7 +4342,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U65" s="3" t="s">
         <v>70</v>
@@ -4341,7 +4359,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4377,7 +4395,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>70</v>
@@ -4394,7 +4412,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4430,7 +4448,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U67" s="3" t="s">
         <v>70</v>
@@ -4447,7 +4465,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4483,7 +4501,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U68" s="3" t="s">
         <v>70</v>
@@ -4494,7 +4512,7 @@
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4503,7 +4521,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4539,7 +4557,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U69" s="3" t="s">
         <v>70</v>
@@ -4556,7 +4574,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4592,7 +4610,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U70" s="3" t="s">
         <v>70</v>
@@ -4609,7 +4627,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4645,7 +4663,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U71" s="3" t="s">
         <v>70</v>
@@ -4662,7 +4680,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4698,7 +4716,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>70</v>
@@ -4715,7 +4733,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4751,7 +4769,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U73" s="3" t="s">
         <v>70</v>
@@ -4768,7 +4786,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4804,7 +4822,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U74" s="3" t="s">
         <v>70</v>
@@ -4821,7 +4839,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4857,7 +4875,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U75" s="3" t="s">
         <v>70</v>
@@ -4874,7 +4892,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4910,7 +4928,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>70</v>
@@ -4927,7 +4945,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4963,7 +4981,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U77" s="3" t="s">
         <v>70</v>
@@ -4980,7 +4998,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -5016,7 +5034,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U78" s="3" t="s">
         <v>70</v>
@@ -5027,7 +5045,7 @@
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5036,7 +5054,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5073,7 +5091,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U79" s="3" t="s">
         <v>70</v>
@@ -5090,7 +5108,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5127,7 +5145,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U80" s="3" t="s">
         <v>70</v>
@@ -5144,7 +5162,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5181,7 +5199,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>70</v>
@@ -5198,7 +5216,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5235,7 +5253,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U82" s="3" t="s">
         <v>70</v>
@@ -5252,7 +5270,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5289,7 +5307,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>70</v>
@@ -5306,7 +5324,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5343,7 +5361,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U84" s="3" t="s">
         <v>70</v>
@@ -5360,7 +5378,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5397,7 +5415,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U85" s="3" t="s">
         <v>70</v>
@@ -5414,7 +5432,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5451,7 +5469,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U86" s="3" t="s">
         <v>70</v>
@@ -5468,7 +5486,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5505,7 +5523,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U87" s="3" t="s">
         <v>70</v>
@@ -5522,7 +5540,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5559,7 +5577,7 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U88" s="3" t="s">
         <v>70</v>
@@ -5567,7 +5585,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>100</v>
@@ -6320,7 +6338,7 @@
         <v>110</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F102" s="3">
         <v>8.0</v>
@@ -6536,6 +6554,984 @@
         <v>57</v>
       </c>
       <c r="U105" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F106" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G106" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I106" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J106" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K106" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L106" s="1">
+        <f>5*4-1</f>
+        <v>19</v>
+      </c>
+      <c r="M106" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N106" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O106" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P106" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q106" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R106" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S106" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U106" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F107" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="G107" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I107" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J107" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K107" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L107" s="1">
+        <f>6*4-1</f>
+        <v>23</v>
+      </c>
+      <c r="M107" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N107" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O107" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P107" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q107" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R107" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S107" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U107" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F108" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I108" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J108" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K108" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L108" s="3">
+        <f>7*4-1</f>
+        <v>27</v>
+      </c>
+      <c r="M108" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N108" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O108" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P108" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q108" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R108" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S108" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U108" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F109" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I109" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J109" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K109" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L109" s="3">
+        <f>8*4-1</f>
+        <v>31</v>
+      </c>
+      <c r="M109" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N109" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O109" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P109" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q109" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R109" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S109" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U109" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F110" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="G110" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I110" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J110" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K110" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L110" s="3">
+        <f>9*4-1</f>
+        <v>35</v>
+      </c>
+      <c r="M110" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N110" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O110" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P110" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q110" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R110" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S110" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T110" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U110" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C111" s="4"/>
+      <c r="E111" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F111" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G111" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I111" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="J111" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K111" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L111" s="1">
+        <f>10*4-1</f>
+        <v>39</v>
+      </c>
+      <c r="M111" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N111" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O111" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P111" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q111" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R111" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S111" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T111" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U111" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C112" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F112" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="G112" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I112" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J112" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K112" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L112" s="1">
+        <f>5*4-1</f>
+        <v>19</v>
+      </c>
+      <c r="M112" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N112" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O112" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P112" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q112" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R112" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S112" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T112" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U112" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C113" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F113" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="G113" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I113" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J113" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K113" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L113" s="1">
+        <f>6*4-1</f>
+        <v>23</v>
+      </c>
+      <c r="M113" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N113" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O113" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P113" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q113" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R113" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S113" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T113" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U113" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C114" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F114" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G114" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I114" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J114" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K114" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L114" s="3">
+        <f>7*4-1</f>
+        <v>27</v>
+      </c>
+      <c r="M114" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N114" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O114" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P114" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q114" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R114" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S114" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T114" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U114" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C115" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F115" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G115" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I115" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J115" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K115" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L115" s="3">
+        <f>8*4-1</f>
+        <v>31</v>
+      </c>
+      <c r="M115" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N115" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O115" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P115" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q115" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R115" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S115" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T115" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U115" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C116" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F116" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="G116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I116" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J116" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K116" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L116" s="3">
+        <f>9*4-1</f>
+        <v>35</v>
+      </c>
+      <c r="M116" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N116" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O116" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P116" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q116" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R116" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S116" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T116" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U116" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C117" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F117" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I117" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="J117" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K117" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L117" s="1">
+        <f>10*4-1</f>
+        <v>39</v>
+      </c>
+      <c r="M117" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N117" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O117" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P117" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q117" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R117" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S117" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T117" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U117" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F118" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="G118" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I118" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J118" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K118" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L118" s="1">
+        <f>6*4-1</f>
+        <v>23</v>
+      </c>
+      <c r="M118" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O118" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P118" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R118" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T118" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U118" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="E119" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F119" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="G119" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I119" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J119" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K119" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L119" s="1">
+        <f>7*4-1</f>
+        <v>27</v>
+      </c>
+      <c r="M119" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O119" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P119" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q119" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R119" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T119" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U119" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="E120" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F120" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="G120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I120" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="J120" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K120" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L120" s="1">
+        <f>8*4-1</f>
+        <v>31</v>
+      </c>
+      <c r="M120" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O120" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P120" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q120" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R120" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T120" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U120" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="E121" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F121" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="G121" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I121" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J121" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="K121" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L121" s="1">
+        <f>4*9-1</f>
+        <v>35</v>
+      </c>
+      <c r="M121" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O121" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P121" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q121" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R121" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U121" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="E122" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F122" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G122" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I122" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J122" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K122" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L122" s="3">
+        <v>39.0</v>
+      </c>
+      <c r="M122" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N122" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O122" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P122" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R122" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S122" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U122" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6561,26 +7557,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -7602,7 +8598,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -7618,26 +8614,26 @@
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -7650,87 +8646,87 @@
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>48</v>
@@ -7754,7 +8750,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>53</v>
@@ -7762,7 +8758,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,72 +15,72 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="121">
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
     <t>Project</t>
   </si>
   <si>
-    <t>Setting</t>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
+    <t>Phase</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
+    <t>Plan</t>
+  </si>
+  <si>
     <t>EGP</t>
   </si>
   <si>
-    <t>Plan</t>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
+  </si>
+  <si>
+    <t>Down Payment 1 %</t>
   </si>
   <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
+    <t>Installments Count</t>
+  </si>
+  <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Installments Count</t>
-  </si>
-  <si>
     <t>Installment Every (months)</t>
   </si>
   <si>
@@ -99,43 +99,43 @@
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Meaning / المعنى</t>
   </si>
   <si>
     <t>YOUD</t>
   </si>
   <si>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+  </si>
+  <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
     <t>Original Price</t>
-  </si>
-  <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
-  </si>
-  <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
@@ -675,31 +675,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>18</v>
@@ -708,7 +708,7 @@
         <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>22</v>
@@ -732,21 +732,21 @@
         <v>22</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -813,7 +813,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -871,7 +871,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -929,7 +929,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -986,7 +986,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1043,7 +1043,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1100,7 +1100,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1214,7 +1214,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1274,7 +1274,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1333,7 +1333,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1381,7 +1381,7 @@
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1390,7 +1390,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1448,7 +1448,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1506,7 +1506,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1564,7 +1564,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1622,7 +1622,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1680,7 +1680,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1738,7 +1738,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1796,7 +1796,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1854,7 +1854,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1912,7 +1912,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1970,7 +1970,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -2026,7 +2026,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -2082,7 +2082,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -2138,7 +2138,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2194,7 +2194,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2250,7 +2250,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2306,7 +2306,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2418,7 +2418,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2475,7 +2475,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2531,7 +2531,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2587,7 +2587,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2643,7 +2643,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2699,7 +2699,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2755,7 +2755,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2906,7 +2906,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U39" s="3" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2962,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>58</v>
@@ -2982,7 +2982,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -3018,7 +3018,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>58</v>
@@ -3038,7 +3038,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3074,7 +3074,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>58</v>
@@ -3094,7 +3094,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3130,7 +3130,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>58</v>
@@ -3436,7 +3436,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3445,7 +3445,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3482,7 +3482,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>70</v>
@@ -3499,7 +3499,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3536,7 +3536,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>70</v>
@@ -3553,7 +3553,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3590,7 +3590,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>70</v>
@@ -3607,7 +3607,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3644,7 +3644,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>70</v>
@@ -3661,7 +3661,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3698,7 +3698,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U53" s="3" t="s">
         <v>70</v>
@@ -3715,7 +3715,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3752,7 +3752,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>70</v>
@@ -3769,7 +3769,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3806,7 +3806,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U55" s="3" t="s">
         <v>70</v>
@@ -3823,7 +3823,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3860,7 +3860,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U56" s="3" t="s">
         <v>70</v>
@@ -3877,7 +3877,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3914,7 +3914,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>70</v>
@@ -3931,7 +3931,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3968,7 +3968,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>70</v>
@@ -3979,7 +3979,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3988,7 +3988,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -4024,7 +4024,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>70</v>
@@ -4041,7 +4041,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4077,7 +4077,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>70</v>
@@ -4094,7 +4094,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4130,7 +4130,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>70</v>
@@ -4147,7 +4147,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4183,7 +4183,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>70</v>
@@ -4200,7 +4200,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4236,7 +4236,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U63" s="3" t="s">
         <v>70</v>
@@ -4253,7 +4253,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4289,7 +4289,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U64" s="3" t="s">
         <v>70</v>
@@ -4306,7 +4306,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4342,7 +4342,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U65" s="3" t="s">
         <v>70</v>
@@ -4359,7 +4359,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4395,7 +4395,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>70</v>
@@ -4412,7 +4412,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4448,7 +4448,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U67" s="3" t="s">
         <v>70</v>
@@ -4465,7 +4465,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4501,7 +4501,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U68" s="3" t="s">
         <v>70</v>
@@ -4512,7 +4512,7 @@
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4521,7 +4521,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4557,7 +4557,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U69" s="3" t="s">
         <v>70</v>
@@ -4574,7 +4574,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4610,7 +4610,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U70" s="3" t="s">
         <v>70</v>
@@ -4627,7 +4627,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4663,7 +4663,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U71" s="3" t="s">
         <v>70</v>
@@ -4680,7 +4680,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4716,7 +4716,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>70</v>
@@ -4733,7 +4733,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4769,7 +4769,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U73" s="3" t="s">
         <v>70</v>
@@ -4786,7 +4786,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4822,7 +4822,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U74" s="3" t="s">
         <v>70</v>
@@ -4839,7 +4839,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4875,7 +4875,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U75" s="3" t="s">
         <v>70</v>
@@ -4892,7 +4892,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4928,7 +4928,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>70</v>
@@ -4945,7 +4945,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4981,7 +4981,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U77" s="3" t="s">
         <v>70</v>
@@ -4998,7 +4998,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -5034,7 +5034,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U78" s="3" t="s">
         <v>70</v>
@@ -5045,7 +5045,7 @@
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5054,7 +5054,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5091,7 +5091,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U79" s="3" t="s">
         <v>70</v>
@@ -5108,7 +5108,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5145,7 +5145,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U80" s="3" t="s">
         <v>70</v>
@@ -5162,7 +5162,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5199,7 +5199,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>70</v>
@@ -5216,7 +5216,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5253,7 +5253,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U82" s="3" t="s">
         <v>70</v>
@@ -5270,7 +5270,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5307,7 +5307,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>70</v>
@@ -5324,7 +5324,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5361,7 +5361,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U84" s="3" t="s">
         <v>70</v>
@@ -5378,7 +5378,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5415,7 +5415,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U85" s="3" t="s">
         <v>70</v>
@@ -5432,7 +5432,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5469,7 +5469,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U86" s="3" t="s">
         <v>70</v>
@@ -5486,7 +5486,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5523,7 +5523,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U87" s="3" t="s">
         <v>70</v>
@@ -5540,7 +5540,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5577,7 +5577,7 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U88" s="3" t="s">
         <v>70</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>100</v>
@@ -6133,8 +6133,8 @@
       <c r="L98" s="1">
         <v>1.0</v>
       </c>
-      <c r="M98" s="1">
-        <v>3.0</v>
+      <c r="M98" s="3">
+        <v>0.0</v>
       </c>
       <c r="N98" s="1">
         <v>6.0</v>
@@ -6192,8 +6192,8 @@
       <c r="L99" s="1">
         <v>1.0</v>
       </c>
-      <c r="M99" s="1">
-        <v>3.0</v>
+      <c r="M99" s="3">
+        <v>0.0</v>
       </c>
       <c r="N99" s="1">
         <v>6.0</v>
@@ -6338,7 +6338,7 @@
         <v>110</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F102" s="3">
         <v>8.0</v>
@@ -6574,7 +6574,7 @@
         <v>15.0</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I106" s="3">
         <v>5.0</v>
@@ -6611,7 +6611,7 @@
         <v>6.0</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U106" s="3" t="s">
         <v>70</v>
@@ -6631,7 +6631,7 @@
         <v>10.0</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I107" s="3">
         <v>5.0</v>
@@ -6668,7 +6668,7 @@
         <v>6.0</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U107" s="3" t="s">
         <v>70</v>
@@ -6688,7 +6688,7 @@
         <v>0.0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I108" s="3">
         <v>5.0</v>
@@ -6725,7 +6725,7 @@
         <v>6.0</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U108" s="3" t="s">
         <v>70</v>
@@ -6745,7 +6745,7 @@
         <v>0.0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I109" s="3">
         <v>10.0</v>
@@ -6782,7 +6782,7 @@
         <v>6.0</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U109" s="3" t="s">
         <v>70</v>
@@ -6802,7 +6802,7 @@
         <v>0.0</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I110" s="3">
         <v>10.0</v>
@@ -6839,7 +6839,7 @@
         <v>6.0</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U110" s="3" t="s">
         <v>70</v>
@@ -6860,7 +6860,7 @@
         <v>0.0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I111" s="3">
         <v>15.0</v>
@@ -6897,7 +6897,7 @@
         <v>6.0</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U111" s="3" t="s">
         <v>70</v>
@@ -6920,7 +6920,7 @@
         <v>15.0</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I112" s="3">
         <v>5.0</v>
@@ -6957,7 +6957,7 @@
         <v>6.0</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U112" s="3" t="s">
         <v>70</v>
@@ -6980,7 +6980,7 @@
         <v>10.0</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I113" s="3">
         <v>5.0</v>
@@ -7017,7 +7017,7 @@
         <v>6.0</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U113" s="3" t="s">
         <v>70</v>
@@ -7040,7 +7040,7 @@
         <v>0.0</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I114" s="3">
         <v>5.0</v>
@@ -7077,7 +7077,7 @@
         <v>6.0</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U114" s="3" t="s">
         <v>70</v>
@@ -7100,7 +7100,7 @@
         <v>0.0</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I115" s="3">
         <v>10.0</v>
@@ -7137,7 +7137,7 @@
         <v>6.0</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U115" s="3" t="s">
         <v>70</v>
@@ -7160,7 +7160,7 @@
         <v>0.0</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I116" s="3">
         <v>10.0</v>
@@ -7197,7 +7197,7 @@
         <v>6.0</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U116" s="3" t="s">
         <v>70</v>
@@ -7220,7 +7220,7 @@
         <v>0.0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I117" s="3">
         <v>15.0</v>
@@ -7257,7 +7257,7 @@
         <v>6.0</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U117" s="3" t="s">
         <v>70</v>
@@ -7277,7 +7277,7 @@
         <v>15.0</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I118" s="3">
         <v>5.0</v>
@@ -7314,7 +7314,7 @@
         <v>6.0</v>
       </c>
       <c r="T118" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U118" s="3" t="s">
         <v>70</v>
@@ -7331,7 +7331,7 @@
         <v>10.0</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I119" s="3">
         <v>5.0</v>
@@ -7368,7 +7368,7 @@
         <v>6.0</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U119" s="3" t="s">
         <v>70</v>
@@ -7385,7 +7385,7 @@
         <v>0.0</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I120" s="3">
         <v>5.0</v>
@@ -7422,7 +7422,7 @@
         <v>6.0</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U120" s="3" t="s">
         <v>70</v>
@@ -7439,7 +7439,7 @@
         <v>0.0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I121" s="3">
         <v>10.0</v>
@@ -7476,7 +7476,7 @@
         <v>6.0</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U121" s="3" t="s">
         <v>70</v>
@@ -7493,7 +7493,7 @@
         <v>0.0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I122" s="3">
         <v>10.0</v>
@@ -7529,7 +7529,7 @@
         <v>6.0</v>
       </c>
       <c r="T122" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="U122" s="3" t="s">
         <v>70</v>
@@ -7557,18 +7557,18 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
@@ -7576,7 +7576,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -8598,79 +8598,79 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>41</v>
@@ -8678,7 +8678,7 @@
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>42</v>
@@ -8686,7 +8686,7 @@
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>43</v>
@@ -8710,7 +8710,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>46</v>
@@ -8766,10 +8766,10 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,60 +15,63 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="121">
   <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
     <t>Setting</t>
   </si>
   <si>
-    <t>How to fill the Projects sheet</t>
-  </si>
-  <si>
-    <t>Project</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Type</t>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Plan</t>
   </si>
   <si>
     <t>Company Name</t>
   </si>
   <si>
-    <t>BUA</t>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t/>
+    <t>Discount %</t>
   </si>
   <si>
     <t>Currency</t>
   </si>
   <si>
-    <t>Plan</t>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
   </si>
   <si>
     <t>EGP</t>
   </si>
   <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
@@ -78,7 +81,43 @@
     <t>Installments Count</t>
   </si>
   <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Meaning / المعنى</t>
+  </si>
+  <si>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+  </si>
+  <si>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+  </si>
+  <si>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
+  </si>
+  <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
+  </si>
+  <si>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
     <t>Installment Every (months)</t>
@@ -87,103 +126,64 @@
     <t>First Installment Due (months)</t>
   </si>
   <si>
+    <t>Number of equal installments / عدد الأقساط</t>
+  </si>
+  <si>
     <t>Maintenance %</t>
   </si>
   <si>
+    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
+  </si>
+  <si>
     <t>Delivery (months)</t>
   </si>
   <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
+  </si>
+  <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+    <t>Admin Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم إدارية</t>
   </si>
   <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+    <t>Operations Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم تشغيل</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
+    <t>% of system price, due at delivery / وديعة الصيانة</t>
   </si>
   <si>
     <t>YOUD</t>
   </si>
   <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+    <t>After editing: save the file, then refresh the page in the browser.</t>
+  </si>
+  <si>
+    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
   </si>
   <si>
     <t>Original Price</t>
-  </si>
-  <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
-  </si>
-  <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
-    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
-  </si>
-  <si>
-    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
-  </si>
-  <si>
-    <t>Admin Fee %</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم إدارية</t>
-  </si>
-  <si>
-    <t>Operations Fee %</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم تشغيل</t>
-  </si>
-  <si>
-    <t>% of system price, due at delivery / وديعة الصيانة</t>
-  </si>
-  <si>
-    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
-  </si>
-  <si>
-    <t>After editing: save the file, then refresh the page in the browser.</t>
-  </si>
-  <si>
-    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
   </si>
   <si>
     <t>Selling price</t>
@@ -675,78 +675,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -813,7 +813,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -871,7 +871,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -929,7 +929,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -986,7 +986,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1043,7 +1043,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1100,7 +1100,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1214,7 +1214,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1274,7 +1274,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1333,7 +1333,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1381,7 +1381,7 @@
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1390,7 +1390,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1448,7 +1448,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1506,7 +1506,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1564,7 +1564,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1622,7 +1622,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1680,7 +1680,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1738,7 +1738,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1796,7 +1796,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1854,7 +1854,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1912,7 +1912,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1970,7 +1970,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -2026,7 +2026,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -2082,7 +2082,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -2138,7 +2138,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2194,7 +2194,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2250,7 +2250,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2306,7 +2306,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2418,7 +2418,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2475,7 +2475,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2531,7 +2531,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2587,7 +2587,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2643,7 +2643,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2699,7 +2699,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2755,7 +2755,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2906,7 +2906,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U39" s="3" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2962,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>58</v>
@@ -2982,7 +2982,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -3018,7 +3018,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>58</v>
@@ -3038,7 +3038,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3074,7 +3074,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>58</v>
@@ -3094,7 +3094,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3130,7 +3130,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>58</v>
@@ -3436,7 +3436,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3445,7 +3445,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3482,7 +3482,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>70</v>
@@ -3499,7 +3499,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3536,7 +3536,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>70</v>
@@ -3553,7 +3553,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3590,7 +3590,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>70</v>
@@ -3607,7 +3607,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3644,7 +3644,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>70</v>
@@ -3661,7 +3661,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3698,7 +3698,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U53" s="3" t="s">
         <v>70</v>
@@ -3715,7 +3715,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3752,7 +3752,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>70</v>
@@ -3769,7 +3769,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3806,7 +3806,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U55" s="3" t="s">
         <v>70</v>
@@ -3823,7 +3823,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3860,7 +3860,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U56" s="3" t="s">
         <v>70</v>
@@ -3877,7 +3877,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3914,7 +3914,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>70</v>
@@ -3931,7 +3931,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3968,7 +3968,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>70</v>
@@ -3979,7 +3979,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3988,7 +3988,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -4024,7 +4024,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>70</v>
@@ -4041,7 +4041,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4077,7 +4077,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>70</v>
@@ -4094,7 +4094,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4130,7 +4130,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>70</v>
@@ -4147,7 +4147,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4183,7 +4183,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>70</v>
@@ -4200,7 +4200,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4236,7 +4236,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U63" s="3" t="s">
         <v>70</v>
@@ -4253,7 +4253,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4289,7 +4289,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U64" s="3" t="s">
         <v>70</v>
@@ -4306,7 +4306,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4342,7 +4342,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U65" s="3" t="s">
         <v>70</v>
@@ -4359,7 +4359,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4395,7 +4395,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>70</v>
@@ -4412,7 +4412,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4448,7 +4448,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U67" s="3" t="s">
         <v>70</v>
@@ -4465,7 +4465,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4501,7 +4501,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U68" s="3" t="s">
         <v>70</v>
@@ -4512,7 +4512,7 @@
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4521,7 +4521,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4557,7 +4557,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U69" s="3" t="s">
         <v>70</v>
@@ -4574,7 +4574,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4610,7 +4610,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U70" s="3" t="s">
         <v>70</v>
@@ -4627,7 +4627,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4663,7 +4663,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U71" s="3" t="s">
         <v>70</v>
@@ -4680,7 +4680,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4716,7 +4716,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>70</v>
@@ -4733,7 +4733,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4769,7 +4769,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U73" s="3" t="s">
         <v>70</v>
@@ -4786,7 +4786,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4822,7 +4822,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U74" s="3" t="s">
         <v>70</v>
@@ -4839,7 +4839,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4875,7 +4875,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U75" s="3" t="s">
         <v>70</v>
@@ -4892,7 +4892,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4928,7 +4928,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>70</v>
@@ -4945,7 +4945,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4981,7 +4981,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U77" s="3" t="s">
         <v>70</v>
@@ -4998,7 +4998,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -5034,7 +5034,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U78" s="3" t="s">
         <v>70</v>
@@ -5045,7 +5045,7 @@
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5054,7 +5054,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5091,7 +5091,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U79" s="3" t="s">
         <v>70</v>
@@ -5108,7 +5108,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5145,7 +5145,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U80" s="3" t="s">
         <v>70</v>
@@ -5162,7 +5162,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5199,7 +5199,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>70</v>
@@ -5216,7 +5216,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5253,7 +5253,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U82" s="3" t="s">
         <v>70</v>
@@ -5270,7 +5270,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5307,7 +5307,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>70</v>
@@ -5324,7 +5324,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5361,7 +5361,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U84" s="3" t="s">
         <v>70</v>
@@ -5378,7 +5378,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5415,7 +5415,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U85" s="3" t="s">
         <v>70</v>
@@ -5432,7 +5432,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5469,7 +5469,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U86" s="3" t="s">
         <v>70</v>
@@ -5486,7 +5486,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5523,7 +5523,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U87" s="3" t="s">
         <v>70</v>
@@ -5540,7 +5540,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5577,7 +5577,7 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U88" s="3" t="s">
         <v>70</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>100</v>
@@ -6121,11 +6121,11 @@
       <c r="H98" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I98" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="J98" s="1">
-        <v>25.0</v>
+      <c r="I98" s="3">
+        <v>50.0</v>
+      </c>
+      <c r="J98" s="3">
+        <v>50.0</v>
       </c>
       <c r="K98" s="1">
         <v>3.0</v>
@@ -6180,11 +6180,11 @@
       <c r="H99" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I99" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="J99" s="1">
-        <v>25.0</v>
+      <c r="I99" s="3">
+        <v>50.0</v>
+      </c>
+      <c r="J99" s="3">
+        <v>50.0</v>
       </c>
       <c r="K99" s="1">
         <v>3.0</v>
@@ -6338,7 +6338,7 @@
         <v>110</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F102" s="3">
         <v>8.0</v>
@@ -6574,7 +6574,7 @@
         <v>15.0</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I106" s="3">
         <v>5.0</v>
@@ -6611,7 +6611,7 @@
         <v>6.0</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U106" s="3" t="s">
         <v>70</v>
@@ -6631,7 +6631,7 @@
         <v>10.0</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I107" s="3">
         <v>5.0</v>
@@ -6668,7 +6668,7 @@
         <v>6.0</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U107" s="3" t="s">
         <v>70</v>
@@ -6688,7 +6688,7 @@
         <v>0.0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I108" s="3">
         <v>5.0</v>
@@ -6725,7 +6725,7 @@
         <v>6.0</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U108" s="3" t="s">
         <v>70</v>
@@ -6745,7 +6745,7 @@
         <v>0.0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I109" s="3">
         <v>10.0</v>
@@ -6782,7 +6782,7 @@
         <v>6.0</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U109" s="3" t="s">
         <v>70</v>
@@ -6802,7 +6802,7 @@
         <v>0.0</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I110" s="3">
         <v>10.0</v>
@@ -6839,7 +6839,7 @@
         <v>6.0</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U110" s="3" t="s">
         <v>70</v>
@@ -6860,7 +6860,7 @@
         <v>0.0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I111" s="3">
         <v>15.0</v>
@@ -6897,7 +6897,7 @@
         <v>6.0</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U111" s="3" t="s">
         <v>70</v>
@@ -6920,7 +6920,7 @@
         <v>15.0</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I112" s="3">
         <v>5.0</v>
@@ -6957,7 +6957,7 @@
         <v>6.0</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U112" s="3" t="s">
         <v>70</v>
@@ -6980,7 +6980,7 @@
         <v>10.0</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I113" s="3">
         <v>5.0</v>
@@ -7017,7 +7017,7 @@
         <v>6.0</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U113" s="3" t="s">
         <v>70</v>
@@ -7040,7 +7040,7 @@
         <v>0.0</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I114" s="3">
         <v>5.0</v>
@@ -7077,7 +7077,7 @@
         <v>6.0</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U114" s="3" t="s">
         <v>70</v>
@@ -7100,7 +7100,7 @@
         <v>0.0</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I115" s="3">
         <v>10.0</v>
@@ -7137,7 +7137,7 @@
         <v>6.0</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U115" s="3" t="s">
         <v>70</v>
@@ -7160,7 +7160,7 @@
         <v>0.0</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I116" s="3">
         <v>10.0</v>
@@ -7197,7 +7197,7 @@
         <v>6.0</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U116" s="3" t="s">
         <v>70</v>
@@ -7220,7 +7220,7 @@
         <v>0.0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I117" s="3">
         <v>15.0</v>
@@ -7257,7 +7257,7 @@
         <v>6.0</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U117" s="3" t="s">
         <v>70</v>
@@ -7277,7 +7277,7 @@
         <v>15.0</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I118" s="3">
         <v>5.0</v>
@@ -7314,7 +7314,7 @@
         <v>6.0</v>
       </c>
       <c r="T118" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U118" s="3" t="s">
         <v>70</v>
@@ -7331,7 +7331,7 @@
         <v>10.0</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I119" s="3">
         <v>5.0</v>
@@ -7368,7 +7368,7 @@
         <v>6.0</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U119" s="3" t="s">
         <v>70</v>
@@ -7385,7 +7385,7 @@
         <v>0.0</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I120" s="3">
         <v>5.0</v>
@@ -7422,7 +7422,7 @@
         <v>6.0</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U120" s="3" t="s">
         <v>70</v>
@@ -7439,7 +7439,7 @@
         <v>0.0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I121" s="3">
         <v>10.0</v>
@@ -7476,7 +7476,7 @@
         <v>6.0</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U121" s="3" t="s">
         <v>70</v>
@@ -7493,7 +7493,7 @@
         <v>0.0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="I122" s="3">
         <v>10.0</v>
@@ -7529,7 +7529,7 @@
         <v>6.0</v>
       </c>
       <c r="T122" s="1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="U122" s="3" t="s">
         <v>70</v>
@@ -7557,26 +7557,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -8601,183 +8601,183 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,22 +15,52 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="121">
   <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
+  </si>
+  <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>Project</t>
   </si>
   <si>
-    <t>How to fill the Projects sheet</t>
-  </si>
-  <si>
-    <t>Setting</t>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Value</t>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
   </si>
   <si>
     <t>BUA</t>
@@ -39,39 +69,33 @@
     <t>Phase</t>
   </si>
   <si>
+    <t>Column</t>
+  </si>
+  <si>
     <t>Plan</t>
   </si>
   <si>
-    <t>Company Name</t>
+    <t>Meaning / المعنى</t>
   </si>
   <si>
     <t>Years</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
     <t>Discount %</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
-    <t>EGP</t>
-  </si>
-  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+  </si>
+  <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
@@ -81,33 +105,33 @@
     <t>Installments Count</t>
   </si>
   <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
-  </si>
-  <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
-  </si>
-  <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
-  </si>
-  <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
+  </si>
+  <si>
+    <t>Delivery (months)</t>
+  </si>
+  <si>
+    <t>First Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance Basis</t>
   </si>
   <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
@@ -117,43 +141,28 @@
     <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
+    <t>YOUD</t>
+  </si>
+  <si>
     <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
     <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
-    <t>Maintenance %</t>
-  </si>
-  <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
   </si>
   <si>
-    <t>Ending Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Admin Fee %</t>
   </si>
   <si>
     <t>% of system price, paid upfront / رسوم إدارية</t>
   </si>
   <si>
-    <t>Maintenance Basis</t>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
     <t>Operations Fee %</t>
@@ -162,28 +171,19 @@
     <t>% of system price, paid upfront / رسوم تشغيل</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>Original Price</t>
   </si>
   <si>
     <t>% of system price, due at delivery / وديعة الصيانة</t>
   </si>
   <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
     <t>After editing: save the file, then refresh the page in the browser.</t>
   </si>
   <si>
     <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
-  </si>
-  <si>
-    <t>Original Price</t>
   </si>
   <si>
     <t>Selling price</t>
@@ -675,78 +675,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -813,7 +813,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -871,7 +871,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -929,7 +929,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -986,7 +986,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1043,7 +1043,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1100,7 +1100,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1214,7 +1214,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1274,7 +1274,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1333,7 +1333,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1381,7 +1381,7 @@
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1390,7 +1390,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1448,7 +1448,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1506,7 +1506,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1564,7 +1564,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1622,7 +1622,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1680,7 +1680,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1738,7 +1738,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1796,7 +1796,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1854,7 +1854,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1912,7 +1912,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1970,7 +1970,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -2026,7 +2026,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -2082,7 +2082,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -2138,7 +2138,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2194,7 +2194,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2250,7 +2250,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2306,7 +2306,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2418,7 +2418,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2475,7 +2475,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2531,7 +2531,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2587,7 +2587,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2643,7 +2643,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2699,7 +2699,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2755,7 +2755,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2906,7 +2906,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U39" s="3" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2962,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>58</v>
@@ -2982,7 +2982,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -3018,7 +3018,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>58</v>
@@ -3038,7 +3038,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3074,7 +3074,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>58</v>
@@ -3094,7 +3094,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3130,7 +3130,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>58</v>
@@ -3436,7 +3436,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3445,7 +3445,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3482,7 +3482,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>70</v>
@@ -3499,7 +3499,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3536,7 +3536,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>70</v>
@@ -3553,7 +3553,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3590,7 +3590,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>70</v>
@@ -3607,7 +3607,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3644,7 +3644,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>70</v>
@@ -3661,7 +3661,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3698,7 +3698,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U53" s="3" t="s">
         <v>70</v>
@@ -3715,7 +3715,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3752,7 +3752,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>70</v>
@@ -3769,7 +3769,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3806,7 +3806,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U55" s="3" t="s">
         <v>70</v>
@@ -3823,7 +3823,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3860,7 +3860,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U56" s="3" t="s">
         <v>70</v>
@@ -3877,7 +3877,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3914,7 +3914,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>70</v>
@@ -3931,7 +3931,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3968,7 +3968,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>70</v>
@@ -3979,7 +3979,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3988,7 +3988,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -4024,7 +4024,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>70</v>
@@ -4041,7 +4041,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4077,7 +4077,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>70</v>
@@ -4094,7 +4094,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4130,7 +4130,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>70</v>
@@ -4147,7 +4147,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4183,7 +4183,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>70</v>
@@ -4200,7 +4200,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4236,7 +4236,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U63" s="3" t="s">
         <v>70</v>
@@ -4253,7 +4253,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4289,7 +4289,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U64" s="3" t="s">
         <v>70</v>
@@ -4306,7 +4306,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4342,7 +4342,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U65" s="3" t="s">
         <v>70</v>
@@ -4359,7 +4359,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4395,7 +4395,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>70</v>
@@ -4412,7 +4412,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4448,7 +4448,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U67" s="3" t="s">
         <v>70</v>
@@ -4465,7 +4465,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4501,7 +4501,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U68" s="3" t="s">
         <v>70</v>
@@ -4512,7 +4512,7 @@
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4521,7 +4521,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4557,7 +4557,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U69" s="3" t="s">
         <v>70</v>
@@ -4574,7 +4574,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4610,7 +4610,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U70" s="3" t="s">
         <v>70</v>
@@ -4627,7 +4627,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4663,7 +4663,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U71" s="3" t="s">
         <v>70</v>
@@ -4680,7 +4680,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4716,7 +4716,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>70</v>
@@ -4733,7 +4733,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4769,7 +4769,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U73" s="3" t="s">
         <v>70</v>
@@ -4786,7 +4786,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4822,7 +4822,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U74" s="3" t="s">
         <v>70</v>
@@ -4839,7 +4839,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4875,7 +4875,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U75" s="3" t="s">
         <v>70</v>
@@ -4892,7 +4892,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4928,7 +4928,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>70</v>
@@ -4945,7 +4945,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4981,7 +4981,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U77" s="3" t="s">
         <v>70</v>
@@ -4998,7 +4998,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -5034,7 +5034,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U78" s="3" t="s">
         <v>70</v>
@@ -5045,7 +5045,7 @@
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5054,7 +5054,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5091,7 +5091,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U79" s="3" t="s">
         <v>70</v>
@@ -5108,7 +5108,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5145,7 +5145,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U80" s="3" t="s">
         <v>70</v>
@@ -5162,7 +5162,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5199,7 +5199,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>70</v>
@@ -5216,7 +5216,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5253,7 +5253,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U82" s="3" t="s">
         <v>70</v>
@@ -5270,7 +5270,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5307,7 +5307,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>70</v>
@@ -5324,7 +5324,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5361,7 +5361,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U84" s="3" t="s">
         <v>70</v>
@@ -5378,7 +5378,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5415,7 +5415,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U85" s="3" t="s">
         <v>70</v>
@@ -5432,7 +5432,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5469,7 +5469,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U86" s="3" t="s">
         <v>70</v>
@@ -5486,7 +5486,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5523,7 +5523,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U87" s="3" t="s">
         <v>70</v>
@@ -5540,7 +5540,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5577,7 +5577,7 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U88" s="3" t="s">
         <v>70</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>100</v>
@@ -6134,7 +6134,7 @@
         <v>1.0</v>
       </c>
       <c r="M98" s="3">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N98" s="1">
         <v>6.0</v>
@@ -6193,7 +6193,7 @@
         <v>1.0</v>
       </c>
       <c r="M99" s="3">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N99" s="1">
         <v>6.0</v>
@@ -6338,7 +6338,7 @@
         <v>110</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F102" s="3">
         <v>8.0</v>
@@ -6574,7 +6574,7 @@
         <v>15.0</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I106" s="3">
         <v>5.0</v>
@@ -6611,7 +6611,7 @@
         <v>6.0</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U106" s="3" t="s">
         <v>70</v>
@@ -6631,7 +6631,7 @@
         <v>10.0</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I107" s="3">
         <v>5.0</v>
@@ -6668,7 +6668,7 @@
         <v>6.0</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U107" s="3" t="s">
         <v>70</v>
@@ -6688,7 +6688,7 @@
         <v>0.0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I108" s="3">
         <v>5.0</v>
@@ -6725,7 +6725,7 @@
         <v>6.0</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U108" s="3" t="s">
         <v>70</v>
@@ -6745,7 +6745,7 @@
         <v>0.0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I109" s="3">
         <v>10.0</v>
@@ -6782,7 +6782,7 @@
         <v>6.0</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U109" s="3" t="s">
         <v>70</v>
@@ -6802,7 +6802,7 @@
         <v>0.0</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I110" s="3">
         <v>10.0</v>
@@ -6839,7 +6839,7 @@
         <v>6.0</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U110" s="3" t="s">
         <v>70</v>
@@ -6860,7 +6860,7 @@
         <v>0.0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I111" s="3">
         <v>15.0</v>
@@ -6897,7 +6897,7 @@
         <v>6.0</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U111" s="3" t="s">
         <v>70</v>
@@ -6920,7 +6920,7 @@
         <v>15.0</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I112" s="3">
         <v>5.0</v>
@@ -6957,7 +6957,7 @@
         <v>6.0</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U112" s="3" t="s">
         <v>70</v>
@@ -6980,7 +6980,7 @@
         <v>10.0</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I113" s="3">
         <v>5.0</v>
@@ -7017,7 +7017,7 @@
         <v>6.0</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U113" s="3" t="s">
         <v>70</v>
@@ -7040,7 +7040,7 @@
         <v>0.0</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I114" s="3">
         <v>5.0</v>
@@ -7077,7 +7077,7 @@
         <v>6.0</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U114" s="3" t="s">
         <v>70</v>
@@ -7100,7 +7100,7 @@
         <v>0.0</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I115" s="3">
         <v>10.0</v>
@@ -7137,7 +7137,7 @@
         <v>6.0</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U115" s="3" t="s">
         <v>70</v>
@@ -7160,7 +7160,7 @@
         <v>0.0</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I116" s="3">
         <v>10.0</v>
@@ -7197,7 +7197,7 @@
         <v>6.0</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U116" s="3" t="s">
         <v>70</v>
@@ -7220,7 +7220,7 @@
         <v>0.0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I117" s="3">
         <v>15.0</v>
@@ -7257,7 +7257,7 @@
         <v>6.0</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U117" s="3" t="s">
         <v>70</v>
@@ -7277,7 +7277,7 @@
         <v>15.0</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I118" s="3">
         <v>5.0</v>
@@ -7314,7 +7314,7 @@
         <v>6.0</v>
       </c>
       <c r="T118" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U118" s="3" t="s">
         <v>70</v>
@@ -7331,7 +7331,7 @@
         <v>10.0</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I119" s="3">
         <v>5.0</v>
@@ -7368,7 +7368,7 @@
         <v>6.0</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U119" s="3" t="s">
         <v>70</v>
@@ -7385,7 +7385,7 @@
         <v>0.0</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I120" s="3">
         <v>5.0</v>
@@ -7422,7 +7422,7 @@
         <v>6.0</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U120" s="3" t="s">
         <v>70</v>
@@ -7439,7 +7439,7 @@
         <v>0.0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I121" s="3">
         <v>10.0</v>
@@ -7476,7 +7476,7 @@
         <v>6.0</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U121" s="3" t="s">
         <v>70</v>
@@ -7493,7 +7493,7 @@
         <v>0.0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I122" s="3">
         <v>10.0</v>
@@ -7529,7 +7529,7 @@
         <v>6.0</v>
       </c>
       <c r="T122" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="U122" s="3" t="s">
         <v>70</v>
@@ -7557,10 +7557,10 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
@@ -7568,7 +7568,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
@@ -7576,7 +7576,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -8598,186 +8598,186 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,123 +15,132 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="121">
   <si>
+    <t>Project</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
+  </si>
+  <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
+    <t>Down Payment 2 %</t>
+  </si>
+  <si>
+    <t>DP2 Due (months)</t>
+  </si>
+  <si>
+    <t>Installments Count</t>
+  </si>
+  <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Setting</t>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
+  </si>
+  <si>
+    <t>Delivery (months)</t>
+  </si>
+  <si>
+    <t>First Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Company Name</t>
   </si>
   <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
+    <t>Maintenance Basis</t>
+  </si>
+  <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>Company Name</t>
+    <t>Currency</t>
   </si>
   <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
-    <t>Type</t>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>EGP</t>
   </si>
   <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t>Phase</t>
+    <t>YOUD</t>
   </si>
   <si>
     <t>Column</t>
   </si>
   <si>
-    <t>Plan</t>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
     <t>Meaning / المعنى</t>
   </si>
   <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
+    <t>Original Price</t>
   </si>
   <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
-    <t>Down Payment 2 %</t>
-  </si>
-  <si>
-    <t>DP2 Due (months)</t>
-  </si>
-  <si>
-    <t>Installments Count</t>
-  </si>
-  <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
-    <t>Maintenance %</t>
-  </si>
-  <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
-    <t>Ending Installment Maintenance Due (months)</t>
-  </si>
-  <si>
-    <t>Maintenance Basis</t>
-  </si>
-  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
@@ -141,9 +150,6 @@
     <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
@@ -162,16 +168,10 @@
     <t>% of system price, paid upfront / رسوم إدارية</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
     <t>Operations Fee %</t>
   </si>
   <si>
     <t>% of system price, paid upfront / رسوم تشغيل</t>
-  </si>
-  <si>
-    <t>Original Price</t>
   </si>
   <si>
     <t>% of system price, due at delivery / وديعة الصيانة</t>
@@ -675,78 +675,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -813,7 +813,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -871,7 +871,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -929,7 +929,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -986,7 +986,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1043,7 +1043,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1100,7 +1100,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1214,7 +1214,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1274,7 +1274,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1333,7 +1333,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1381,7 +1381,7 @@
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1390,7 +1390,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1448,7 +1448,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1506,7 +1506,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1564,7 +1564,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1622,7 +1622,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1680,7 +1680,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1738,7 +1738,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1796,7 +1796,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1854,7 +1854,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1912,7 +1912,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1970,7 +1970,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -2026,7 +2026,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -2082,7 +2082,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -2138,7 +2138,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2194,7 +2194,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2250,7 +2250,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2306,7 +2306,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2418,7 +2418,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2475,7 +2475,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2531,7 +2531,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2587,7 +2587,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2643,7 +2643,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2699,7 +2699,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2755,7 +2755,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2906,7 +2906,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U39" s="3" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2962,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>58</v>
@@ -2982,7 +2982,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -3018,7 +3018,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>58</v>
@@ -3038,7 +3038,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3074,7 +3074,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>58</v>
@@ -3094,7 +3094,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3130,7 +3130,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>58</v>
@@ -3436,7 +3436,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3445,7 +3445,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3482,7 +3482,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>70</v>
@@ -3499,7 +3499,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3536,7 +3536,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>70</v>
@@ -3553,7 +3553,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3590,7 +3590,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>70</v>
@@ -3607,7 +3607,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3644,7 +3644,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>70</v>
@@ -3661,7 +3661,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3698,7 +3698,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U53" s="3" t="s">
         <v>70</v>
@@ -3715,7 +3715,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3752,7 +3752,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>70</v>
@@ -3769,7 +3769,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3806,7 +3806,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U55" s="3" t="s">
         <v>70</v>
@@ -3823,7 +3823,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3860,7 +3860,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U56" s="3" t="s">
         <v>70</v>
@@ -3877,7 +3877,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3914,7 +3914,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>70</v>
@@ -3931,7 +3931,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3968,7 +3968,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>70</v>
@@ -3979,7 +3979,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3988,7 +3988,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -4024,7 +4024,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>70</v>
@@ -4041,7 +4041,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4077,7 +4077,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>70</v>
@@ -4094,7 +4094,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4130,7 +4130,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>70</v>
@@ -4147,7 +4147,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4183,7 +4183,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>70</v>
@@ -4200,7 +4200,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4236,7 +4236,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U63" s="3" t="s">
         <v>70</v>
@@ -4253,7 +4253,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4289,7 +4289,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U64" s="3" t="s">
         <v>70</v>
@@ -4306,7 +4306,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4342,7 +4342,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U65" s="3" t="s">
         <v>70</v>
@@ -4359,7 +4359,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4395,7 +4395,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>70</v>
@@ -4412,7 +4412,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4448,7 +4448,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U67" s="3" t="s">
         <v>70</v>
@@ -4465,7 +4465,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4501,7 +4501,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U68" s="3" t="s">
         <v>70</v>
@@ -4512,7 +4512,7 @@
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4521,7 +4521,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4557,7 +4557,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U69" s="3" t="s">
         <v>70</v>
@@ -4574,7 +4574,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4610,7 +4610,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U70" s="3" t="s">
         <v>70</v>
@@ -4627,7 +4627,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4663,7 +4663,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U71" s="3" t="s">
         <v>70</v>
@@ -4680,7 +4680,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4716,7 +4716,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>70</v>
@@ -4733,7 +4733,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4769,7 +4769,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U73" s="3" t="s">
         <v>70</v>
@@ -4786,7 +4786,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4822,7 +4822,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U74" s="3" t="s">
         <v>70</v>
@@ -4839,7 +4839,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4875,7 +4875,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U75" s="3" t="s">
         <v>70</v>
@@ -4892,7 +4892,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4928,7 +4928,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>70</v>
@@ -4945,7 +4945,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4981,7 +4981,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U77" s="3" t="s">
         <v>70</v>
@@ -4998,7 +4998,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -5034,7 +5034,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U78" s="3" t="s">
         <v>70</v>
@@ -5045,7 +5045,7 @@
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5054,7 +5054,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5091,7 +5091,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U79" s="3" t="s">
         <v>70</v>
@@ -5108,7 +5108,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5145,7 +5145,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U80" s="3" t="s">
         <v>70</v>
@@ -5162,7 +5162,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5199,7 +5199,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>70</v>
@@ -5216,7 +5216,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5253,7 +5253,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U82" s="3" t="s">
         <v>70</v>
@@ -5270,7 +5270,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5307,7 +5307,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>70</v>
@@ -5324,7 +5324,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5361,7 +5361,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U84" s="3" t="s">
         <v>70</v>
@@ -5378,7 +5378,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5415,7 +5415,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U85" s="3" t="s">
         <v>70</v>
@@ -5432,7 +5432,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5469,7 +5469,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U86" s="3" t="s">
         <v>70</v>
@@ -5486,7 +5486,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5523,7 +5523,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U87" s="3" t="s">
         <v>70</v>
@@ -5540,7 +5540,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5577,7 +5577,7 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U88" s="3" t="s">
         <v>70</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>100</v>
@@ -6134,7 +6134,7 @@
         <v>1.0</v>
       </c>
       <c r="M98" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N98" s="1">
         <v>6.0</v>
@@ -6193,7 +6193,7 @@
         <v>1.0</v>
       </c>
       <c r="M99" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N99" s="1">
         <v>6.0</v>
@@ -6338,7 +6338,7 @@
         <v>110</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F102" s="3">
         <v>8.0</v>
@@ -6574,7 +6574,7 @@
         <v>15.0</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I106" s="3">
         <v>5.0</v>
@@ -6611,7 +6611,7 @@
         <v>6.0</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U106" s="3" t="s">
         <v>70</v>
@@ -6631,7 +6631,7 @@
         <v>10.0</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I107" s="3">
         <v>5.0</v>
@@ -6668,7 +6668,7 @@
         <v>6.0</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U107" s="3" t="s">
         <v>70</v>
@@ -6688,7 +6688,7 @@
         <v>0.0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I108" s="3">
         <v>5.0</v>
@@ -6725,7 +6725,7 @@
         <v>6.0</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U108" s="3" t="s">
         <v>70</v>
@@ -6745,7 +6745,7 @@
         <v>0.0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I109" s="3">
         <v>10.0</v>
@@ -6782,7 +6782,7 @@
         <v>6.0</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U109" s="3" t="s">
         <v>70</v>
@@ -6802,7 +6802,7 @@
         <v>0.0</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I110" s="3">
         <v>10.0</v>
@@ -6839,7 +6839,7 @@
         <v>6.0</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U110" s="3" t="s">
         <v>70</v>
@@ -6860,7 +6860,7 @@
         <v>0.0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I111" s="3">
         <v>15.0</v>
@@ -6897,7 +6897,7 @@
         <v>6.0</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U111" s="3" t="s">
         <v>70</v>
@@ -6920,7 +6920,7 @@
         <v>15.0</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I112" s="3">
         <v>5.0</v>
@@ -6957,7 +6957,7 @@
         <v>6.0</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U112" s="3" t="s">
         <v>70</v>
@@ -6980,7 +6980,7 @@
         <v>10.0</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I113" s="3">
         <v>5.0</v>
@@ -7017,7 +7017,7 @@
         <v>6.0</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U113" s="3" t="s">
         <v>70</v>
@@ -7040,7 +7040,7 @@
         <v>0.0</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I114" s="3">
         <v>5.0</v>
@@ -7077,7 +7077,7 @@
         <v>6.0</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U114" s="3" t="s">
         <v>70</v>
@@ -7100,7 +7100,7 @@
         <v>0.0</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I115" s="3">
         <v>10.0</v>
@@ -7137,7 +7137,7 @@
         <v>6.0</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U115" s="3" t="s">
         <v>70</v>
@@ -7160,7 +7160,7 @@
         <v>0.0</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I116" s="3">
         <v>10.0</v>
@@ -7197,7 +7197,7 @@
         <v>6.0</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U116" s="3" t="s">
         <v>70</v>
@@ -7220,7 +7220,7 @@
         <v>0.0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I117" s="3">
         <v>15.0</v>
@@ -7257,7 +7257,7 @@
         <v>6.0</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U117" s="3" t="s">
         <v>70</v>
@@ -7277,7 +7277,7 @@
         <v>15.0</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I118" s="3">
         <v>5.0</v>
@@ -7314,7 +7314,7 @@
         <v>6.0</v>
       </c>
       <c r="T118" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U118" s="3" t="s">
         <v>70</v>
@@ -7331,7 +7331,7 @@
         <v>10.0</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I119" s="3">
         <v>5.0</v>
@@ -7368,7 +7368,7 @@
         <v>6.0</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U119" s="3" t="s">
         <v>70</v>
@@ -7385,7 +7385,7 @@
         <v>0.0</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I120" s="3">
         <v>5.0</v>
@@ -7422,7 +7422,7 @@
         <v>6.0</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U120" s="3" t="s">
         <v>70</v>
@@ -7439,7 +7439,7 @@
         <v>0.0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I121" s="3">
         <v>10.0</v>
@@ -7476,7 +7476,7 @@
         <v>6.0</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U121" s="3" t="s">
         <v>70</v>
@@ -7493,7 +7493,7 @@
         <v>0.0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I122" s="3">
         <v>10.0</v>
@@ -7529,7 +7529,7 @@
         <v>6.0</v>
       </c>
       <c r="T122" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="U122" s="3" t="s">
         <v>70</v>
@@ -7557,26 +7557,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -8598,159 +8598,159 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>53</v>
@@ -8758,7 +8758,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
@@ -8766,10 +8766,10 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -36,133 +36,133 @@
     <t>BUA</t>
   </si>
   <si>
+    <t>Company Name</t>
+  </si>
+  <si>
     <t>Phase</t>
   </si>
   <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
+  </si>
+  <si>
     <t>Plan</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
     <t>Years</t>
   </si>
   <si>
+    <t>EGP</t>
+  </si>
+  <si>
     <t>Discount %</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+  </si>
+  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
+    <t>Column</t>
   </si>
   <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
+    <t>Meaning / المعنى</t>
+  </si>
+  <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+  </si>
+  <si>
     <t>Installments Count</t>
   </si>
   <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
     <t>Installment Every (months)</t>
   </si>
   <si>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+  </si>
+  <si>
     <t>First Installment Due (months)</t>
   </si>
   <si>
     <t>Maintenance %</t>
   </si>
   <si>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
+  </si>
+  <si>
     <t>Delivery (months)</t>
   </si>
   <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
-  </si>
-  <si>
-    <t>Alahly Sabbour</t>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
   </si>
   <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+  </si>
+  <si>
+    <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
     <t>YOUD</t>
   </si>
   <si>
-    <t>Column</t>
+    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>Meaning / المعنى</t>
+    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
+  </si>
+  <si>
+    <t>Admin Fee %</t>
   </si>
   <si>
     <t>Original Price</t>
-  </si>
-  <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
-  </si>
-  <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
-  </si>
-  <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
-  </si>
-  <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
-    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
-  </si>
-  <si>
-    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
-  </si>
-  <si>
-    <t>Admin Fee %</t>
   </si>
   <si>
     <t>% of system price, paid upfront / رسوم إدارية</t>
@@ -684,69 +684,69 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -755,7 +755,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -813,7 +813,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -871,7 +871,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -929,7 +929,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -986,7 +986,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1043,7 +1043,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1100,7 +1100,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1157,7 +1157,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1214,7 +1214,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1274,7 +1274,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1333,7 +1333,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1381,7 +1381,7 @@
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1390,7 +1390,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1448,7 +1448,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1506,7 +1506,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1564,7 +1564,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1622,7 +1622,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1680,7 +1680,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1738,7 +1738,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1796,7 +1796,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1854,7 +1854,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1912,7 +1912,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1970,7 +1970,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -2026,7 +2026,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -2082,7 +2082,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -2138,7 +2138,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2194,7 +2194,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2250,7 +2250,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2306,7 +2306,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2418,7 +2418,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2475,7 +2475,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2531,7 +2531,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2587,7 +2587,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2643,7 +2643,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2699,7 +2699,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2755,7 +2755,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2906,7 +2906,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U39" s="3" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2962,7 +2962,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U40" s="3" t="s">
         <v>58</v>
@@ -2982,7 +2982,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -3018,7 +3018,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>58</v>
@@ -3038,7 +3038,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3074,7 +3074,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>58</v>
@@ -3094,7 +3094,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3130,7 +3130,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>58</v>
@@ -3436,7 +3436,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3445,7 +3445,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3482,7 +3482,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>70</v>
@@ -3499,7 +3499,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3536,7 +3536,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U50" s="3" t="s">
         <v>70</v>
@@ -3553,7 +3553,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3590,7 +3590,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U51" s="3" t="s">
         <v>70</v>
@@ -3607,7 +3607,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3644,7 +3644,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>70</v>
@@ -3661,7 +3661,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3698,7 +3698,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U53" s="3" t="s">
         <v>70</v>
@@ -3715,7 +3715,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3752,7 +3752,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>70</v>
@@ -3769,7 +3769,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3806,7 +3806,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U55" s="3" t="s">
         <v>70</v>
@@ -3823,7 +3823,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3860,7 +3860,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U56" s="3" t="s">
         <v>70</v>
@@ -3877,7 +3877,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3914,7 +3914,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>70</v>
@@ -3931,7 +3931,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3968,7 +3968,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>70</v>
@@ -3979,7 +3979,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3988,7 +3988,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -4024,7 +4024,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>70</v>
@@ -4041,7 +4041,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4077,7 +4077,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>70</v>
@@ -4094,7 +4094,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4130,7 +4130,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U61" s="3" t="s">
         <v>70</v>
@@ -4147,7 +4147,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4183,7 +4183,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>70</v>
@@ -4200,7 +4200,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4236,7 +4236,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U63" s="3" t="s">
         <v>70</v>
@@ -4253,7 +4253,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4289,7 +4289,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U64" s="3" t="s">
         <v>70</v>
@@ -4306,7 +4306,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4342,7 +4342,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U65" s="3" t="s">
         <v>70</v>
@@ -4359,7 +4359,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4395,7 +4395,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>70</v>
@@ -4412,7 +4412,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4448,7 +4448,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U67" s="3" t="s">
         <v>70</v>
@@ -4465,7 +4465,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4501,7 +4501,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U68" s="3" t="s">
         <v>70</v>
@@ -4512,7 +4512,7 @@
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4521,7 +4521,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4557,7 +4557,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U69" s="3" t="s">
         <v>70</v>
@@ -4574,7 +4574,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4610,7 +4610,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U70" s="3" t="s">
         <v>70</v>
@@ -4627,7 +4627,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4663,7 +4663,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U71" s="3" t="s">
         <v>70</v>
@@ -4680,7 +4680,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4716,7 +4716,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>70</v>
@@ -4733,7 +4733,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4769,7 +4769,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U73" s="3" t="s">
         <v>70</v>
@@ -4786,7 +4786,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4822,7 +4822,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U74" s="3" t="s">
         <v>70</v>
@@ -4839,7 +4839,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4875,7 +4875,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U75" s="3" t="s">
         <v>70</v>
@@ -4892,7 +4892,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4928,7 +4928,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>70</v>
@@ -4945,7 +4945,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4981,7 +4981,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U77" s="3" t="s">
         <v>70</v>
@@ -4998,7 +4998,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -5034,7 +5034,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U78" s="3" t="s">
         <v>70</v>
@@ -5045,7 +5045,7 @@
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5054,7 +5054,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5091,7 +5091,7 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U79" s="3" t="s">
         <v>70</v>
@@ -5108,7 +5108,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5145,7 +5145,7 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U80" s="3" t="s">
         <v>70</v>
@@ -5162,7 +5162,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5199,7 +5199,7 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>70</v>
@@ -5216,7 +5216,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5253,7 +5253,7 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U82" s="3" t="s">
         <v>70</v>
@@ -5270,7 +5270,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5307,7 +5307,7 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>70</v>
@@ -5324,7 +5324,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5361,7 +5361,7 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U84" s="3" t="s">
         <v>70</v>
@@ -5378,7 +5378,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5415,7 +5415,7 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U85" s="3" t="s">
         <v>70</v>
@@ -5432,7 +5432,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5469,7 +5469,7 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U86" s="3" t="s">
         <v>70</v>
@@ -5486,7 +5486,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5523,7 +5523,7 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U87" s="3" t="s">
         <v>70</v>
@@ -5540,7 +5540,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5577,7 +5577,7 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U88" s="3" t="s">
         <v>70</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>100</v>
@@ -6134,7 +6134,7 @@
         <v>1.0</v>
       </c>
       <c r="M98" s="3">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N98" s="1">
         <v>6.0</v>
@@ -6193,7 +6193,7 @@
         <v>1.0</v>
       </c>
       <c r="M99" s="3">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="N99" s="1">
         <v>6.0</v>
@@ -6338,7 +6338,7 @@
         <v>110</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F102" s="3">
         <v>8.0</v>
@@ -6574,7 +6574,7 @@
         <v>15.0</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I106" s="3">
         <v>5.0</v>
@@ -6611,7 +6611,7 @@
         <v>6.0</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U106" s="3" t="s">
         <v>70</v>
@@ -6631,7 +6631,7 @@
         <v>10.0</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I107" s="3">
         <v>5.0</v>
@@ -6668,7 +6668,7 @@
         <v>6.0</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U107" s="3" t="s">
         <v>70</v>
@@ -6688,7 +6688,7 @@
         <v>0.0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I108" s="3">
         <v>5.0</v>
@@ -6725,7 +6725,7 @@
         <v>6.0</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U108" s="3" t="s">
         <v>70</v>
@@ -6745,7 +6745,7 @@
         <v>0.0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I109" s="3">
         <v>10.0</v>
@@ -6782,7 +6782,7 @@
         <v>6.0</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U109" s="3" t="s">
         <v>70</v>
@@ -6802,7 +6802,7 @@
         <v>0.0</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I110" s="3">
         <v>10.0</v>
@@ -6839,7 +6839,7 @@
         <v>6.0</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U110" s="3" t="s">
         <v>70</v>
@@ -6860,7 +6860,7 @@
         <v>0.0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I111" s="3">
         <v>15.0</v>
@@ -6897,7 +6897,7 @@
         <v>6.0</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U111" s="3" t="s">
         <v>70</v>
@@ -6920,7 +6920,7 @@
         <v>15.0</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I112" s="3">
         <v>5.0</v>
@@ -6957,7 +6957,7 @@
         <v>6.0</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U112" s="3" t="s">
         <v>70</v>
@@ -6980,7 +6980,7 @@
         <v>10.0</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I113" s="3">
         <v>5.0</v>
@@ -7017,7 +7017,7 @@
         <v>6.0</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U113" s="3" t="s">
         <v>70</v>
@@ -7040,7 +7040,7 @@
         <v>0.0</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I114" s="3">
         <v>5.0</v>
@@ -7077,7 +7077,7 @@
         <v>6.0</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U114" s="3" t="s">
         <v>70</v>
@@ -7100,7 +7100,7 @@
         <v>0.0</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I115" s="3">
         <v>10.0</v>
@@ -7137,7 +7137,7 @@
         <v>6.0</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U115" s="3" t="s">
         <v>70</v>
@@ -7160,7 +7160,7 @@
         <v>0.0</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I116" s="3">
         <v>10.0</v>
@@ -7197,7 +7197,7 @@
         <v>6.0</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U116" s="3" t="s">
         <v>70</v>
@@ -7220,7 +7220,7 @@
         <v>0.0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I117" s="3">
         <v>15.0</v>
@@ -7257,7 +7257,7 @@
         <v>6.0</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U117" s="3" t="s">
         <v>70</v>
@@ -7277,7 +7277,7 @@
         <v>15.0</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I118" s="3">
         <v>5.0</v>
@@ -7314,7 +7314,7 @@
         <v>6.0</v>
       </c>
       <c r="T118" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U118" s="3" t="s">
         <v>70</v>
@@ -7331,7 +7331,7 @@
         <v>10.0</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I119" s="3">
         <v>5.0</v>
@@ -7368,7 +7368,7 @@
         <v>6.0</v>
       </c>
       <c r="T119" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U119" s="3" t="s">
         <v>70</v>
@@ -7385,7 +7385,7 @@
         <v>0.0</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I120" s="3">
         <v>5.0</v>
@@ -7422,7 +7422,7 @@
         <v>6.0</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U120" s="3" t="s">
         <v>70</v>
@@ -7439,7 +7439,7 @@
         <v>0.0</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I121" s="3">
         <v>10.0</v>
@@ -7476,7 +7476,7 @@
         <v>6.0</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U121" s="3" t="s">
         <v>70</v>
@@ -7493,7 +7493,7 @@
         <v>0.0</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="I122" s="3">
         <v>10.0</v>
@@ -7529,7 +7529,7 @@
         <v>6.0</v>
       </c>
       <c r="T122" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="U122" s="3" t="s">
         <v>70</v>
@@ -7565,18 +7565,18 @@
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -8614,7 +8614,7 @@
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>17</v>
@@ -8622,18 +8622,18 @@
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -8646,10 +8646,10 @@
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -8657,84 +8657,84 @@
         <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>50</v>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>53</v>
@@ -8758,7 +8758,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,59 +13,104 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="122">
   <si>
     <t>Project</t>
   </si>
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
+  </si>
+  <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
+    <t>Down Payment 2 %</t>
+  </si>
+  <si>
+    <t>DP2 Due (months)</t>
+  </si>
+  <si>
+    <t>Installments Count</t>
+  </si>
+  <si>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
+  </si>
+  <si>
+    <t>Delivery (months)</t>
+  </si>
+  <si>
+    <t>First Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance Basis</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Type</t>
+    <t>YOUD</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Alahly Sabbour</t>
+    <t>Original Price</t>
   </si>
   <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>Plan</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
@@ -81,90 +126,45 @@
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
     <t>Column</t>
   </si>
   <si>
-    <t>Down Payment 2 %</t>
-  </si>
-  <si>
     <t>Meaning / المعنى</t>
   </si>
   <si>
-    <t>DP2 Due (months)</t>
-  </si>
-  <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>Installments Count</t>
-  </si>
-  <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
-    <t>Maintenance %</t>
-  </si>
-  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
-    <t>Ending Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
   </si>
   <si>
-    <t>Maintenance Basis</t>
-  </si>
-  <si>
     <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
     <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
     <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
   </si>
   <si>
     <t>Admin Fee %</t>
   </si>
   <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>% of system price, paid upfront / رسوم إدارية</t>
   </si>
   <si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>15% &amp; 10% &amp; 10 years</t>
+  </si>
+  <si>
+    <t>Clinics</t>
   </si>
   <si>
     <t>The Mornings (Residental)</t>
@@ -681,72 +684,72 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>41</v>
+      <c r="U1" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -755,7 +758,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -795,13 +798,13 @@
       <c r="T2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="U2" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
-        <v>44</v>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>59</v>
@@ -813,7 +816,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -853,13 +856,13 @@
       <c r="T3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="U3" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="s">
-        <v>44</v>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>60</v>
@@ -871,7 +874,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -911,13 +914,13 @@
       <c r="T4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="U4" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="s">
-        <v>44</v>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>61</v>
@@ -929,7 +932,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -952,10 +955,10 @@
       <c r="O5" s="1">
         <v>10.0</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>18.0</v>
       </c>
       <c r="R5" s="1">
@@ -968,13 +971,13 @@
       <c r="T5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="3" t="s">
+      <c r="U5" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="s">
-        <v>44</v>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>62</v>
@@ -986,7 +989,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -1009,10 +1012,10 @@
       <c r="O6" s="1">
         <v>10.0</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>18.0</v>
       </c>
       <c r="R6" s="1">
@@ -1025,13 +1028,13 @@
       <c r="T6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="U6" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="s">
-        <v>44</v>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>63</v>
@@ -1043,7 +1046,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -1066,10 +1069,10 @@
       <c r="O7" s="1">
         <v>10.0</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <v>18.0</v>
       </c>
       <c r="R7" s="1">
@@ -1082,13 +1085,13 @@
       <c r="T7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="U7" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="s">
-        <v>44</v>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>64</v>
@@ -1100,7 +1103,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1123,10 +1126,10 @@
       <c r="O8" s="1">
         <v>10.0</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="2">
         <v>18.0</v>
       </c>
       <c r="R8" s="1">
@@ -1139,13 +1142,13 @@
       <c r="T8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="U8" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="s">
-        <v>44</v>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>65</v>
@@ -1157,7 +1160,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1180,10 +1183,10 @@
       <c r="O9" s="1">
         <v>10.0</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <v>18.0</v>
       </c>
       <c r="R9" s="1">
@@ -1196,13 +1199,13 @@
       <c r="T9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U9" s="3" t="s">
+      <c r="U9" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="s">
-        <v>44</v>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>66</v>
@@ -1214,7 +1217,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1237,10 +1240,10 @@
       <c r="O10" s="1">
         <v>10.0</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <v>18.0</v>
       </c>
       <c r="R10" s="1">
@@ -1253,13 +1256,13 @@
       <c r="T10" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U10" s="3" t="s">
+      <c r="U10" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="s">
-        <v>44</v>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>67</v>
@@ -1274,7 +1277,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1300,10 +1303,10 @@
       <c r="P11" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q11" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="3">
+      <c r="Q11" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R11" s="2">
         <v>18.0</v>
       </c>
       <c r="S11" s="1">
@@ -1312,15 +1315,15 @@
       <c r="T11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U11" s="3" t="s">
+      <c r="U11" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="2">
         <v>4.0</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1333,7 +1336,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1372,16 +1375,16 @@
       <c r="T12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U12" s="3" t="s">
+      <c r="U12" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1390,7 +1393,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1430,12 +1433,12 @@
       <c r="T13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U13" s="3" t="s">
+      <c r="U13" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1448,7 +1451,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1488,12 +1491,12 @@
       <c r="T14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1506,7 +1509,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1546,12 +1549,12 @@
       <c r="T15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="U15" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1564,7 +1567,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1604,12 +1607,12 @@
       <c r="T16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U16" s="3" t="s">
+      <c r="U16" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1622,7 +1625,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1662,12 +1665,12 @@
       <c r="T17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U17" s="3" t="s">
+      <c r="U17" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1680,7 +1683,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1720,12 +1723,12 @@
       <c r="T18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U18" s="3" t="s">
+      <c r="U18" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1738,7 +1741,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1778,12 +1781,12 @@
       <c r="T19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U19" s="3" t="s">
+      <c r="U19" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -1796,7 +1799,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1836,12 +1839,12 @@
       <c r="T20" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U20" s="3" t="s">
+      <c r="U20" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1854,7 +1857,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1894,12 +1897,12 @@
       <c r="T21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U21" s="3" t="s">
+      <c r="U21" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -1912,7 +1915,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1952,7 +1955,7 @@
       <c r="T22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U22" s="3" t="s">
+      <c r="U22" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1970,7 +1973,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -2008,7 +2011,7 @@
       <c r="T23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U23" s="3" t="s">
+      <c r="U23" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2016,7 +2019,7 @@
       <c r="B24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F24" s="1">
@@ -2026,24 +2029,24 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" s="3">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2">
         <v>15.0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="J24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="2">
         <v>12.0</v>
       </c>
       <c r="M24" s="1">
         <v>3.0</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="2">
         <v>3.0</v>
       </c>
       <c r="O24" s="1">
@@ -2064,7 +2067,7 @@
       <c r="T24" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U24" s="3" t="s">
+      <c r="U24" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2072,7 +2075,7 @@
       <c r="B25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F25" s="1">
@@ -2082,24 +2085,24 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I25" s="3">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2">
         <v>20.0</v>
       </c>
-      <c r="J25" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="3">
+      <c r="J25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="2">
         <v>16.0</v>
       </c>
       <c r="M25" s="1">
         <v>3.0</v>
       </c>
-      <c r="N25" s="3">
+      <c r="N25" s="2">
         <v>3.0</v>
       </c>
       <c r="O25" s="1">
@@ -2120,7 +2123,7 @@
       <c r="T25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U25" s="3" t="s">
+      <c r="U25" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2128,7 +2131,7 @@
       <c r="B26" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F26" s="1">
@@ -2138,24 +2141,24 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I26" s="3">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2">
         <v>25.0</v>
       </c>
-      <c r="J26" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="J26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="2">
         <v>20.0</v>
       </c>
       <c r="M26" s="1">
         <v>3.0</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="2">
         <v>3.0</v>
       </c>
       <c r="O26" s="1">
@@ -2176,7 +2179,7 @@
       <c r="T26" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U26" s="3" t="s">
+      <c r="U26" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2184,7 +2187,7 @@
       <c r="B27" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F27" s="1">
@@ -2194,24 +2197,24 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" s="3">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2">
         <v>30.0</v>
       </c>
-      <c r="J27" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="J27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="2">
         <v>24.0</v>
       </c>
       <c r="M27" s="1">
         <v>3.0</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="2">
         <v>3.0</v>
       </c>
       <c r="O27" s="1">
@@ -2232,7 +2235,7 @@
       <c r="T27" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U27" s="3" t="s">
+      <c r="U27" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2240,7 +2243,7 @@
       <c r="B28" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F28" s="1">
@@ -2250,24 +2253,24 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="3">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2">
         <v>35.0</v>
       </c>
-      <c r="J28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="3">
+      <c r="J28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="2">
         <v>28.0</v>
       </c>
       <c r="M28" s="1">
         <v>3.0</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28" s="2">
         <v>3.0</v>
       </c>
       <c r="O28" s="1">
@@ -2288,7 +2291,7 @@
       <c r="T28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U28" s="3" t="s">
+      <c r="U28" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2296,7 +2299,7 @@
       <c r="B29" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F29" s="1">
@@ -2306,24 +2309,24 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I29" s="3">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2">
         <v>40.0</v>
       </c>
-      <c r="J29" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="J29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="2">
         <v>32.0</v>
       </c>
       <c r="M29" s="1">
         <v>3.0</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="2">
         <v>3.0</v>
       </c>
       <c r="O29" s="1">
@@ -2344,7 +2347,7 @@
       <c r="T29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="U29" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2400,456 +2403,456 @@
       <c r="T30" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U30" s="3" t="s">
+      <c r="U30" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>4.0</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="2">
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I31" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="3">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="2">
         <v>0.0</v>
       </c>
       <c r="L31" s="1">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="M31" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N31" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O31" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P31" s="3">
+      <c r="M31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P31" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q31" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R31" s="3">
+      <c r="Q31" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R31" s="2">
         <v>15.0</v>
       </c>
-      <c r="S31" s="3">
+      <c r="S31" s="2">
         <v>3.0</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U31" s="3" t="s">
+      <c r="U31" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>5.0</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="2">
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I32" s="3">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2">
         <v>15.0</v>
       </c>
-      <c r="J32" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="J32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="2">
         <v>20.0</v>
       </c>
-      <c r="M32" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="M32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P32" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q32" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="Q32" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R32" s="2">
         <v>15.0</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="2">
         <v>3.0</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U32" s="3" t="s">
+      <c r="U32" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F33" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="F33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G33" s="2">
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I33" s="3">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2">
         <v>20.0</v>
       </c>
-      <c r="J33" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="J33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="2">
         <v>24.0</v>
       </c>
-      <c r="M33" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N33" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O33" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="M33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P33" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q33" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="Q33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R33" s="2">
         <v>15.0</v>
       </c>
-      <c r="S33" s="3">
+      <c r="S33" s="2">
         <v>3.0</v>
       </c>
       <c r="T33" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U33" s="3" t="s">
+      <c r="U33" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <v>7.0</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="2">
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I34" s="3">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2">
         <v>25.0</v>
       </c>
-      <c r="J34" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="3">
+      <c r="J34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="2">
         <v>28.0</v>
       </c>
-      <c r="M34" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N34" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O34" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P34" s="3">
+      <c r="M34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O34" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P34" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q34" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R34" s="3">
+      <c r="Q34" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R34" s="2">
         <v>15.0</v>
       </c>
-      <c r="S34" s="3">
+      <c r="S34" s="2">
         <v>3.0</v>
       </c>
       <c r="T34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U34" s="3" t="s">
+      <c r="U34" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <v>8.0</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="2">
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I35" s="3">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2">
         <v>30.0</v>
       </c>
-      <c r="J35" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="J35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="2">
         <v>32.0</v>
       </c>
-      <c r="M35" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N35" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O35" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="M35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P35" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q35" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="Q35" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R35" s="2">
         <v>15.0</v>
       </c>
-      <c r="S35" s="3">
+      <c r="S35" s="2">
         <v>3.0</v>
       </c>
       <c r="T35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U35" s="3" t="s">
+      <c r="U35" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>9.0</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="2">
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I36" s="3">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2">
         <v>35.0</v>
       </c>
-      <c r="J36" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="3">
+      <c r="J36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="2">
         <v>36.0</v>
       </c>
-      <c r="M36" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N36" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O36" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P36" s="3">
+      <c r="M36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P36" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q36" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R36" s="3">
+      <c r="Q36" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R36" s="2">
         <v>15.0</v>
       </c>
-      <c r="S36" s="3">
+      <c r="S36" s="2">
         <v>3.0</v>
       </c>
       <c r="T36" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U36" s="3" t="s">
+      <c r="U36" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F37" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G37" s="3">
+      <c r="F37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G37" s="2">
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I37" s="3">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2">
         <v>40.0</v>
       </c>
-      <c r="J37" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L37" s="3">
+      <c r="J37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="2">
         <v>40.0</v>
       </c>
-      <c r="M37" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N37" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O37" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P37" s="3">
+      <c r="M37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P37" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q37" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R37" s="3">
+      <c r="Q37" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R37" s="2">
         <v>15.0</v>
       </c>
-      <c r="S37" s="3">
+      <c r="S37" s="2">
         <v>3.0</v>
       </c>
       <c r="T37" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U37" s="3" t="s">
+      <c r="U37" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>80</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="F38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G38" s="2">
         <v>15.0</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="2">
         <v>100.0</v>
       </c>
-      <c r="J38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P38" s="3">
+      <c r="J38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P38" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q38" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R38" s="3">
+      <c r="Q38" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R38" s="2">
         <v>15.0</v>
       </c>
-      <c r="S38" s="3">
+      <c r="S38" s="2">
         <v>3.0</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U38" s="3" t="s">
+      <c r="U38" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2906,9 +2909,9 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U39" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2926,7 +2929,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2962,9 +2965,9 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U40" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2982,7 +2985,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2993,7 +2996,7 @@
       <c r="K41" s="1">
         <v>3.0</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="2">
         <v>27.0</v>
       </c>
       <c r="M41" s="1">
@@ -3018,9 +3021,9 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U41" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3038,7 +3041,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -3049,7 +3052,7 @@
       <c r="K42" s="1">
         <v>3.0</v>
       </c>
-      <c r="L42" s="3">
+      <c r="L42" s="2">
         <v>23.0</v>
       </c>
       <c r="M42" s="1">
@@ -3074,9 +3077,9 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U42" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3094,7 +3097,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -3105,7 +3108,7 @@
       <c r="K43" s="1">
         <v>3.0</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="2">
         <v>19.0</v>
       </c>
       <c r="M43" s="1">
@@ -3130,9 +3133,9 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U43" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3191,7 +3194,7 @@
       <c r="T44" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U44" s="3" t="s">
+      <c r="U44" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3250,7 +3253,7 @@
       <c r="T45" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U45" s="3" t="s">
+      <c r="U45" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3282,7 +3285,7 @@
       <c r="K46" s="1">
         <v>3.0</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="2">
         <v>27.0</v>
       </c>
       <c r="M46" s="1">
@@ -3309,7 +3312,7 @@
       <c r="T46" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U46" s="3" t="s">
+      <c r="U46" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3341,7 +3344,7 @@
       <c r="K47" s="1">
         <v>3.0</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="2">
         <v>23.0</v>
       </c>
       <c r="M47" s="1">
@@ -3368,7 +3371,7 @@
       <c r="T47" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U47" s="3" t="s">
+      <c r="U47" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3400,7 +3403,7 @@
       <c r="K48" s="1">
         <v>3.0</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="2">
         <v>19.0</v>
       </c>
       <c r="M48" s="1">
@@ -3427,7 +3430,7 @@
       <c r="T48" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U48" s="3" t="s">
+      <c r="U48" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3436,7 +3439,7 @@
         <v>96</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3445,7 +3448,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3482,9 +3485,9 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U49" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3499,7 +3502,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3536,9 +3539,9 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U50" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3553,7 +3556,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3590,9 +3593,9 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U51" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3607,7 +3610,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3644,9 +3647,9 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U52" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3661,7 +3664,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3698,9 +3701,9 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U53" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3715,7 +3718,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3752,9 +3755,9 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U54" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3769,7 +3772,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3806,9 +3809,9 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U55" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3823,7 +3826,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3860,9 +3863,9 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U56" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3877,7 +3880,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3914,9 +3917,9 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U57" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U57" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3931,7 +3934,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3968,9 +3971,9 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U58" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3979,7 +3982,7 @@
         <v>97</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3988,7 +3991,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -4024,9 +4027,9 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U59" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4041,7 +4044,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -4077,9 +4080,9 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U60" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4094,7 +4097,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -4130,9 +4133,9 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U61" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4147,7 +4150,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -4183,9 +4186,9 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U62" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4200,7 +4203,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -4236,9 +4239,9 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U63" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4253,7 +4256,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4289,9 +4292,9 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U64" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4306,7 +4309,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4342,9 +4345,9 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U65" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4359,7 +4362,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4395,9 +4398,9 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U66" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4412,7 +4415,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4448,9 +4451,9 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U67" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4465,7 +4468,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4501,18 +4504,18 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U68" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4521,7 +4524,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4544,22 +4547,22 @@
       <c r="O69" s="1">
         <v>10.0</v>
       </c>
-      <c r="P69" s="3">
+      <c r="P69" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q69" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R69" s="3">
+      <c r="Q69" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R69" s="2">
         <v>30.0</v>
       </c>
-      <c r="S69" s="3">
+      <c r="S69" s="2">
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U69" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4574,7 +4577,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4597,22 +4600,22 @@
       <c r="O70" s="1">
         <v>10.0</v>
       </c>
-      <c r="P70" s="3">
+      <c r="P70" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q70" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R70" s="3">
+      <c r="Q70" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R70" s="2">
         <v>30.0</v>
       </c>
-      <c r="S70" s="3">
+      <c r="S70" s="2">
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U70" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4627,7 +4630,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4650,22 +4653,22 @@
       <c r="O71" s="1">
         <v>10.0</v>
       </c>
-      <c r="P71" s="3">
+      <c r="P71" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q71" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R71" s="3">
+      <c r="Q71" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R71" s="2">
         <v>30.0</v>
       </c>
-      <c r="S71" s="3">
+      <c r="S71" s="2">
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U71" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4680,7 +4683,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4703,22 +4706,22 @@
       <c r="O72" s="1">
         <v>10.0</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q72" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R72" s="3">
+      <c r="Q72" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R72" s="2">
         <v>30.0</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="2">
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U72" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4733,7 +4736,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4756,22 +4759,22 @@
       <c r="O73" s="1">
         <v>10.0</v>
       </c>
-      <c r="P73" s="3">
+      <c r="P73" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q73" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R73" s="3">
+      <c r="Q73" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R73" s="2">
         <v>30.0</v>
       </c>
-      <c r="S73" s="3">
+      <c r="S73" s="2">
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U73" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4786,7 +4789,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4809,22 +4812,22 @@
       <c r="O74" s="1">
         <v>10.0</v>
       </c>
-      <c r="P74" s="3">
+      <c r="P74" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q74" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R74" s="3">
+      <c r="Q74" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R74" s="2">
         <v>30.0</v>
       </c>
-      <c r="S74" s="3">
+      <c r="S74" s="2">
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U74" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4839,7 +4842,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4862,22 +4865,22 @@
       <c r="O75" s="1">
         <v>10.0</v>
       </c>
-      <c r="P75" s="3">
+      <c r="P75" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q75" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R75" s="3">
+      <c r="Q75" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R75" s="2">
         <v>30.0</v>
       </c>
-      <c r="S75" s="3">
+      <c r="S75" s="2">
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U75" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4892,7 +4895,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4915,22 +4918,22 @@
       <c r="O76" s="1">
         <v>10.0</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q76" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R76" s="3">
+      <c r="Q76" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R76" s="2">
         <v>30.0</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="2">
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U76" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4945,7 +4948,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4968,22 +4971,22 @@
       <c r="O77" s="1">
         <v>10.0</v>
       </c>
-      <c r="P77" s="3">
+      <c r="P77" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q77" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R77" s="3">
+      <c r="Q77" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R77" s="2">
         <v>30.0</v>
       </c>
-      <c r="S77" s="3">
+      <c r="S77" s="2">
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U77" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4998,7 +5001,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -5021,31 +5024,31 @@
       <c r="O78" s="1">
         <v>10.0</v>
       </c>
-      <c r="P78" s="3">
+      <c r="P78" s="2">
         <v>24.0</v>
       </c>
-      <c r="Q78" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R78" s="3">
+      <c r="Q78" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R78" s="2">
         <v>30.0</v>
       </c>
-      <c r="S78" s="3">
+      <c r="S78" s="2">
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U78" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F79" s="1">
         <v>8.0</v>
@@ -5054,7 +5057,7 @@
         <v>0.0</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I79" s="1">
         <v>5.0</v>
@@ -5091,9 +5094,9 @@
         <v>6.0</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U79" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5108,7 +5111,7 @@
         <v>10.0</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I80" s="1">
         <v>10.0</v>
@@ -5145,9 +5148,9 @@
         <v>6.0</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U80" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5162,7 +5165,7 @@
         <v>15.0</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I81" s="1">
         <v>7.5</v>
@@ -5199,9 +5202,9 @@
         <v>6.0</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U81" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5216,7 +5219,7 @@
         <v>20.0</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I82" s="1">
         <v>10.0</v>
@@ -5253,9 +5256,9 @@
         <v>6.0</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U82" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5270,7 +5273,7 @@
         <v>25.0</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I83" s="1">
         <v>12.5</v>
@@ -5307,9 +5310,9 @@
         <v>6.0</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U83" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5324,7 +5327,7 @@
         <v>30.0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I84" s="1">
         <v>15.0</v>
@@ -5361,9 +5364,9 @@
         <v>6.0</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U84" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U84" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5378,7 +5381,7 @@
         <v>35.0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I85" s="1">
         <v>17.5</v>
@@ -5415,9 +5418,9 @@
         <v>6.0</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U85" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U85" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5432,7 +5435,7 @@
         <v>40.0</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I86" s="1">
         <v>20.0</v>
@@ -5469,9 +5472,9 @@
         <v>6.0</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U86" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U86" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5486,7 +5489,7 @@
         <v>45.0</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I87" s="1">
         <v>22.5</v>
@@ -5523,9 +5526,9 @@
         <v>6.0</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U87" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U87" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5540,7 +5543,7 @@
         <v>50.0</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I88" s="1">
         <v>25.0</v>
@@ -5577,23 +5580,23 @@
         <v>6.0</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U88" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U88" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B89" s="3" t="s">
+      <c r="A89" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="2">
         <v>10.0</v>
       </c>
       <c r="G89" s="1">
@@ -5611,7 +5614,7 @@
       <c r="K89" s="1">
         <v>3.0</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="2">
         <v>39.0</v>
       </c>
       <c r="M89" s="1">
@@ -5640,18 +5643,18 @@
       <c r="T89" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U89" s="3" t="s">
+      <c r="U89" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90" s="2">
         <v>10.0</v>
       </c>
       <c r="G90" s="1">
@@ -5669,7 +5672,7 @@
       <c r="K90" s="1">
         <v>3.0</v>
       </c>
-      <c r="L90" s="3">
+      <c r="L90" s="2">
         <v>40.0</v>
       </c>
       <c r="M90" s="1">
@@ -5698,18 +5701,18 @@
       <c r="T90" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U90" s="3" t="s">
+      <c r="U90" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91" s="2">
         <v>10.0</v>
       </c>
       <c r="G91" s="1">
@@ -5727,7 +5730,7 @@
       <c r="K91" s="1">
         <v>3.0</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="2">
         <v>39.0</v>
       </c>
       <c r="M91" s="1">
@@ -5756,18 +5759,18 @@
       <c r="T91" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U91" s="3" t="s">
+      <c r="U91" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92" s="2">
         <v>10.0</v>
       </c>
       <c r="G92" s="1">
@@ -5785,7 +5788,7 @@
       <c r="K92" s="1">
         <v>3.0</v>
       </c>
-      <c r="L92" s="3">
+      <c r="L92" s="2">
         <v>39.0</v>
       </c>
       <c r="M92" s="1">
@@ -5797,10 +5800,10 @@
       <c r="O92" s="1">
         <v>10.0</v>
       </c>
-      <c r="P92" s="3">
+      <c r="P92" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q92" s="3">
+      <c r="Q92" s="2">
         <v>18.0</v>
       </c>
       <c r="R92" s="1">
@@ -5813,18 +5816,18 @@
       <c r="T92" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U92" s="3" t="s">
+      <c r="U92" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93" s="2">
         <v>10.0</v>
       </c>
       <c r="G93" s="1">
@@ -5842,7 +5845,7 @@
       <c r="K93" s="1">
         <v>3.0</v>
       </c>
-      <c r="L93" s="3">
+      <c r="L93" s="2">
         <v>39.0</v>
       </c>
       <c r="M93" s="1">
@@ -5854,10 +5857,10 @@
       <c r="O93" s="1">
         <v>10.0</v>
       </c>
-      <c r="P93" s="3">
+      <c r="P93" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q93" s="3">
+      <c r="Q93" s="2">
         <v>18.0</v>
       </c>
       <c r="R93" s="1">
@@ -5870,18 +5873,18 @@
       <c r="T93" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U93" s="3" t="s">
+      <c r="U93" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="2">
         <v>10.0</v>
       </c>
       <c r="G94" s="1">
@@ -5899,7 +5902,7 @@
       <c r="K94" s="1">
         <v>3.0</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="2">
         <v>39.0</v>
       </c>
       <c r="M94" s="1">
@@ -5911,10 +5914,10 @@
       <c r="O94" s="1">
         <v>10.0</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="2">
         <v>18.0</v>
       </c>
       <c r="R94" s="1">
@@ -5927,18 +5930,18 @@
       <c r="T94" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U94" s="3" t="s">
+      <c r="U94" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95" s="2">
         <v>10.0</v>
       </c>
       <c r="G95" s="1">
@@ -5956,7 +5959,7 @@
       <c r="K95" s="1">
         <v>3.0</v>
       </c>
-      <c r="L95" s="3">
+      <c r="L95" s="2">
         <v>39.0</v>
       </c>
       <c r="M95" s="1">
@@ -5968,10 +5971,10 @@
       <c r="O95" s="1">
         <v>10.0</v>
       </c>
-      <c r="P95" s="3">
+      <c r="P95" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q95" s="3">
+      <c r="Q95" s="2">
         <v>18.0</v>
       </c>
       <c r="R95" s="1">
@@ -5984,18 +5987,18 @@
       <c r="T95" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U95" s="3" t="s">
+      <c r="U95" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="2">
         <v>10.0</v>
       </c>
       <c r="G96" s="1">
@@ -6013,7 +6016,7 @@
       <c r="K96" s="1">
         <v>3.0</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="2">
         <v>39.0</v>
       </c>
       <c r="M96" s="1">
@@ -6025,10 +6028,10 @@
       <c r="O96" s="1">
         <v>10.0</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="2">
         <v>18.0</v>
       </c>
       <c r="R96" s="1">
@@ -6041,18 +6044,18 @@
       <c r="T96" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U96" s="3" t="s">
+      <c r="U96" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97" s="2">
         <v>10.0</v>
       </c>
       <c r="G97" s="1">
@@ -6070,7 +6073,7 @@
       <c r="K97" s="1">
         <v>3.0</v>
       </c>
-      <c r="L97" s="3">
+      <c r="L97" s="2">
         <v>39.0</v>
       </c>
       <c r="M97" s="1">
@@ -6082,10 +6085,10 @@
       <c r="O97" s="1">
         <v>10.0</v>
       </c>
-      <c r="P97" s="3">
+      <c r="P97" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q97" s="3">
+      <c r="Q97" s="2">
         <v>18.0</v>
       </c>
       <c r="R97" s="1">
@@ -6098,12 +6101,12 @@
       <c r="T97" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U97" s="3" t="s">
+      <c r="U97" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>100</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -6121,10 +6124,10 @@
       <c r="H98" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I98" s="3">
+      <c r="I98" s="2">
         <v>50.0</v>
       </c>
-      <c r="J98" s="3">
+      <c r="J98" s="2">
         <v>50.0</v>
       </c>
       <c r="K98" s="1">
@@ -6133,7 +6136,7 @@
       <c r="L98" s="1">
         <v>1.0</v>
       </c>
-      <c r="M98" s="3">
+      <c r="M98" s="2">
         <v>3.0</v>
       </c>
       <c r="N98" s="1">
@@ -6145,10 +6148,10 @@
       <c r="P98" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q98" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R98" s="3">
+      <c r="Q98" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R98" s="2">
         <v>18.0</v>
       </c>
       <c r="S98" s="1">
@@ -6157,15 +6160,15 @@
       <c r="T98" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U98" s="3" t="s">
+      <c r="U98" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="2">
         <v>4.0</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -6180,10 +6183,10 @@
       <c r="H99" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I99" s="3">
+      <c r="I99" s="2">
         <v>50.0</v>
       </c>
-      <c r="J99" s="3">
+      <c r="J99" s="2">
         <v>50.0</v>
       </c>
       <c r="K99" s="1">
@@ -6192,7 +6195,7 @@
       <c r="L99" s="1">
         <v>1.0</v>
       </c>
-      <c r="M99" s="3">
+      <c r="M99" s="2">
         <v>3.0</v>
       </c>
       <c r="N99" s="1">
@@ -6217,54 +6220,54 @@
       <c r="T99" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U99" s="3" t="s">
+      <c r="U99" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F100" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="F100" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G100" s="2">
         <v>0.0</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="2">
         <v>5.0</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="2">
         <v>5.0</v>
       </c>
-      <c r="K100" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="K100" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L100" s="2">
         <v>39.0</v>
       </c>
-      <c r="M100" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="M100" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N100" s="2">
         <v>6.0</v>
       </c>
       <c r="O100" s="1">
         <v>10.0</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="2">
         <v>48.0</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="2">
         <v>30.0</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="2">
         <v>42.0</v>
       </c>
       <c r="S100" s="1">
@@ -6273,54 +6276,54 @@
       <c r="T100" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U100" s="3" t="s">
+      <c r="U100" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="2">
         <v>9.0</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="2">
         <v>7.0</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="2">
         <v>5.0</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="2">
         <v>5.0</v>
       </c>
-      <c r="K101" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="K101" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L101" s="2">
         <v>35.0</v>
       </c>
-      <c r="M101" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="M101" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N101" s="2">
         <v>6.0</v>
       </c>
       <c r="O101" s="1">
         <v>10.0</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="2">
         <v>48.0</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="2">
         <v>30.0</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="2">
         <v>42.0</v>
       </c>
       <c r="S101" s="1">
@@ -6329,54 +6332,54 @@
       <c r="T101" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U101" s="3" t="s">
+      <c r="U101" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="E102" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F102" s="2">
         <v>8.0</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="2">
         <v>14.0</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I102" s="3">
+      <c r="I102" s="2">
         <v>5.0</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="2">
         <v>5.0</v>
       </c>
-      <c r="K102" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="K102" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L102" s="2">
         <v>31.0</v>
       </c>
-      <c r="M102" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="M102" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N102" s="2">
         <v>6.0</v>
       </c>
       <c r="O102" s="1">
         <v>10.0</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="2">
         <v>48.0</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="2">
         <v>30.0</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="2">
         <v>42.0</v>
       </c>
       <c r="S102" s="1">
@@ -6385,54 +6388,54 @@
       <c r="T102" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U102" s="3" t="s">
+      <c r="U102" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103" s="2">
         <v>7.0</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103" s="2">
         <v>21.0</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I103" s="3">
+      <c r="I103" s="2">
         <v>5.0</v>
       </c>
-      <c r="J103" s="3">
+      <c r="J103" s="2">
         <v>5.0</v>
       </c>
-      <c r="K103" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L103" s="3">
+      <c r="K103" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L103" s="2">
         <v>27.0</v>
       </c>
-      <c r="M103" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N103" s="3">
+      <c r="M103" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N103" s="2">
         <v>6.0</v>
       </c>
       <c r="O103" s="1">
         <v>10.0</v>
       </c>
-      <c r="P103" s="3">
+      <c r="P103" s="2">
         <v>48.0</v>
       </c>
-      <c r="Q103" s="3">
+      <c r="Q103" s="2">
         <v>30.0</v>
       </c>
-      <c r="R103" s="3">
+      <c r="R103" s="2">
         <v>42.0</v>
       </c>
       <c r="S103" s="1">
@@ -6441,54 +6444,54 @@
       <c r="T103" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U103" s="3" t="s">
+      <c r="U103" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E104" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F104" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G104" s="3">
+      <c r="F104" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G104" s="2">
         <v>28.0</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I104" s="3">
+      <c r="I104" s="2">
         <v>5.0</v>
       </c>
-      <c r="J104" s="3">
+      <c r="J104" s="2">
         <v>5.0</v>
       </c>
-      <c r="K104" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L104" s="3">
+      <c r="K104" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L104" s="2">
         <v>23.0</v>
       </c>
-      <c r="M104" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N104" s="3">
+      <c r="M104" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N104" s="2">
         <v>6.0</v>
       </c>
       <c r="O104" s="1">
         <v>10.0</v>
       </c>
-      <c r="P104" s="3">
+      <c r="P104" s="2">
         <v>48.0</v>
       </c>
-      <c r="Q104" s="3">
+      <c r="Q104" s="2">
         <v>30.0</v>
       </c>
-      <c r="R104" s="3">
+      <c r="R104" s="2">
         <v>42.0</v>
       </c>
       <c r="S104" s="1">
@@ -6497,54 +6500,54 @@
       <c r="T104" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U104" s="3" t="s">
+      <c r="U104" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105" s="2">
         <v>5.0</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105" s="2">
         <v>35.0</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I105" s="3">
+      <c r="I105" s="2">
         <v>5.0</v>
       </c>
-      <c r="J105" s="3">
+      <c r="J105" s="2">
         <v>5.0</v>
       </c>
-      <c r="K105" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L105" s="3">
+      <c r="K105" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L105" s="2">
         <v>19.0</v>
       </c>
-      <c r="M105" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N105" s="3">
+      <c r="M105" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N105" s="2">
         <v>6.0</v>
       </c>
       <c r="O105" s="1">
         <v>10.0</v>
       </c>
-      <c r="P105" s="3">
+      <c r="P105" s="2">
         <v>48.0</v>
       </c>
-      <c r="Q105" s="3">
+      <c r="Q105" s="2">
         <v>30.0</v>
       </c>
-      <c r="R105" s="3">
+      <c r="R105" s="2">
         <v>42.0</v>
       </c>
       <c r="S105" s="1">
@@ -6553,7 +6556,7 @@
       <c r="T105" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U105" s="3" t="s">
+      <c r="U105" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6564,25 +6567,25 @@
       <c r="B106" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E106" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106" s="2">
         <v>5.0</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106" s="2">
         <v>15.0</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I106" s="3">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2">
         <v>5.0</v>
       </c>
-      <c r="J106" s="3">
+      <c r="J106" s="2">
         <v>5.0</v>
       </c>
-      <c r="K106" s="3">
+      <c r="K106" s="2">
         <v>3.0</v>
       </c>
       <c r="L106" s="1">
@@ -6611,9 +6614,9 @@
         <v>6.0</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U106" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U106" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6621,22 +6624,22 @@
       <c r="B107" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F107" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G107" s="3">
+      <c r="F107" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G107" s="2">
         <v>10.0</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I107" s="3">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2">
         <v>5.0</v>
       </c>
-      <c r="J107" s="3">
+      <c r="J107" s="2">
         <v>5.0</v>
       </c>
       <c r="K107" s="1">
@@ -6668,9 +6671,9 @@
         <v>6.0</v>
       </c>
       <c r="T107" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U107" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U107" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6684,22 +6687,22 @@
       <c r="F108" s="1">
         <v>7.0</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108" s="2">
         <v>0.0</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I108" s="3">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2">
         <v>5.0</v>
       </c>
-      <c r="J108" s="3">
+      <c r="J108" s="2">
         <v>5.0</v>
       </c>
       <c r="K108" s="1">
         <v>3.0</v>
       </c>
-      <c r="L108" s="3">
+      <c r="L108" s="2">
         <f>7*4-1</f>
         <v>27</v>
       </c>
@@ -6725,9 +6728,9 @@
         <v>6.0</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U108" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U108" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6735,28 +6738,28 @@
       <c r="B109" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109" s="2">
         <v>8.0</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109" s="2">
         <v>0.0</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I109" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J109" s="3">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J109" s="2">
         <v>5.0</v>
       </c>
       <c r="K109" s="1">
         <v>3.0</v>
       </c>
-      <c r="L109" s="3">
+      <c r="L109" s="2">
         <f>8*4-1</f>
         <v>31</v>
       </c>
@@ -6782,9 +6785,9 @@
         <v>6.0</v>
       </c>
       <c r="T109" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U109" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U109" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6792,28 +6795,28 @@
       <c r="B110" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="E110" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110" s="2">
         <v>9.0</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110" s="2">
         <v>0.0</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I110" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J110" s="3">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J110" s="2">
         <v>10.0</v>
       </c>
       <c r="K110" s="1">
         <v>3.0</v>
       </c>
-      <c r="L110" s="3">
+      <c r="L110" s="2">
         <f>9*4-1</f>
         <v>35</v>
       </c>
@@ -6839,9 +6842,9 @@
         <v>6.0</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U110" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U110" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6850,22 +6853,22 @@
         <v>89</v>
       </c>
       <c r="C111" s="4"/>
-      <c r="E111" s="3" t="s">
+      <c r="E111" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F111" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G111" s="3">
+      <c r="F111" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G111" s="2">
         <v>0.0</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I111" s="3">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2">
         <v>15.0</v>
       </c>
-      <c r="J111" s="3">
+      <c r="J111" s="2">
         <v>10.0</v>
       </c>
       <c r="K111" s="1">
@@ -6897,38 +6900,35 @@
         <v>6.0</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U111" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U111" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C112" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E112" s="3" t="s">
+      <c r="B112" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112" s="2">
         <v>5.0</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112" s="2">
         <v>15.0</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I112" s="3">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2">
         <v>5.0</v>
       </c>
-      <c r="J112" s="3">
+      <c r="J112" s="2">
         <v>5.0</v>
       </c>
-      <c r="K112" s="3">
+      <c r="K112" s="2">
         <v>3.0</v>
       </c>
       <c r="L112" s="1">
@@ -6957,35 +6957,32 @@
         <v>6.0</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U112" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U112" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C113" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E113" s="3" t="s">
+      <c r="B113" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F113" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G113" s="3">
+      <c r="F113" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G113" s="2">
         <v>10.0</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I113" s="3">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2">
         <v>5.0</v>
       </c>
-      <c r="J113" s="3">
+      <c r="J113" s="2">
         <v>5.0</v>
       </c>
       <c r="K113" s="1">
@@ -7017,18 +7014,15 @@
         <v>6.0</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U113" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U113" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C114" s="4">
-        <v>20000.0</v>
+      <c r="B114" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>92</v>
@@ -7036,22 +7030,22 @@
       <c r="F114" s="1">
         <v>7.0</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114" s="2">
         <v>0.0</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I114" s="3">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2">
         <v>5.0</v>
       </c>
-      <c r="J114" s="3">
+      <c r="J114" s="2">
         <v>5.0</v>
       </c>
       <c r="K114" s="1">
         <v>3.0</v>
       </c>
-      <c r="L114" s="3">
+      <c r="L114" s="2">
         <f>7*4-1</f>
         <v>27</v>
       </c>
@@ -7077,41 +7071,38 @@
         <v>6.0</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U114" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U114" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C115" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E115" s="3" t="s">
+      <c r="B115" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115" s="2">
         <v>8.0</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115" s="2">
         <v>0.0</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I115" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J115" s="3">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J115" s="2">
         <v>5.0</v>
       </c>
       <c r="K115" s="1">
         <v>3.0</v>
       </c>
-      <c r="L115" s="3">
+      <c r="L115" s="2">
         <f>8*4-1</f>
         <v>31</v>
       </c>
@@ -7137,41 +7128,38 @@
         <v>6.0</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U115" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U115" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C116" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="B116" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="2">
         <v>9.0</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G116" s="2">
         <v>0.0</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I116" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J116" s="3">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J116" s="2">
         <v>10.0</v>
       </c>
       <c r="K116" s="1">
         <v>3.0</v>
       </c>
-      <c r="L116" s="3">
+      <c r="L116" s="2">
         <f>9*4-1</f>
         <v>35</v>
       </c>
@@ -7197,35 +7185,33 @@
         <v>6.0</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U116" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U116" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C117" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E117" s="3" t="s">
+      <c r="B117" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="E117" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F117" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G117" s="3">
+      <c r="F117" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G117" s="2">
         <v>0.0</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I117" s="3">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2">
         <v>15.0</v>
       </c>
-      <c r="J117" s="3">
+      <c r="J117" s="2">
         <v>10.0</v>
       </c>
       <c r="K117" s="1">
@@ -7257,281 +7243,641 @@
         <v>6.0</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U117" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U117" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E118" s="3" t="s">
+      <c r="B118" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C118" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F118" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G118" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J118" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="K118" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L118" s="1">
+        <f>5*4-1</f>
+        <v>19</v>
+      </c>
+      <c r="M118" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O118" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P118" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R118" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T118" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U118" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C119" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F118" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G118" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I118" s="3">
+      <c r="F119" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G119" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2">
         <v>5.0</v>
       </c>
-      <c r="J118" s="3">
+      <c r="J119" s="2">
         <v>5.0</v>
       </c>
-      <c r="K118" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L118" s="1">
+      <c r="K119" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L119" s="1">
         <f>6*4-1</f>
         <v>23</v>
       </c>
-      <c r="M118" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N118" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O118" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P118" s="1">
+      <c r="M119" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O119" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P119" s="1">
         <v>42.0</v>
       </c>
-      <c r="Q118" s="1">
+      <c r="Q119" s="1">
         <v>15.0</v>
       </c>
-      <c r="R118" s="1">
+      <c r="R119" s="1">
         <v>39.0</v>
       </c>
-      <c r="S118" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T118" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U118" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="E119" s="3" t="s">
+      <c r="S119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T119" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U119" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C120" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F120" s="1">
         <v>7.0</v>
       </c>
-      <c r="G119" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I119" s="3">
+      <c r="G120" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2">
         <v>5.0</v>
       </c>
-      <c r="J119" s="3">
+      <c r="J120" s="2">
         <v>5.0</v>
       </c>
-      <c r="K119" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L119" s="1">
+      <c r="K120" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L120" s="2">
         <f>7*4-1</f>
         <v>27</v>
       </c>
-      <c r="M119" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N119" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O119" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P119" s="1">
+      <c r="M120" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O120" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P120" s="1">
         <v>42.0</v>
       </c>
-      <c r="Q119" s="1">
+      <c r="Q120" s="1">
         <v>15.0</v>
       </c>
-      <c r="R119" s="1">
+      <c r="R120" s="1">
         <v>39.0</v>
       </c>
-      <c r="S119" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T119" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U119" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="E120" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F120" s="3">
+      <c r="S120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U120" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C121" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F121" s="2">
         <v>8.0</v>
       </c>
-      <c r="G120" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I120" s="3">
+      <c r="G121" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J121" s="2">
         <v>5.0</v>
       </c>
-      <c r="J120" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="K120" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L120" s="1">
+      <c r="K121" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L121" s="2">
         <f>8*4-1</f>
         <v>31</v>
       </c>
-      <c r="M120" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N120" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O120" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P120" s="1">
+      <c r="M121" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O121" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P121" s="1">
         <v>42.0</v>
       </c>
-      <c r="Q120" s="1">
+      <c r="Q121" s="1">
         <v>15.0</v>
       </c>
-      <c r="R120" s="1">
+      <c r="R121" s="1">
         <v>39.0</v>
       </c>
-      <c r="S120" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T120" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U120" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="E121" s="3" t="s">
+      <c r="S121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U121" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C122" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F122" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="G122" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J122" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="K122" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L122" s="2">
+        <f>9*4-1</f>
+        <v>35</v>
+      </c>
+      <c r="M122" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N122" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O122" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P122" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R122" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S122" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U122" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C123" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F123" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G123" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="J123" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="K123" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L123" s="1">
+        <f>10*4-1</f>
+        <v>39</v>
+      </c>
+      <c r="M123" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N123" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O123" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P123" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q123" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R123" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S123" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U123" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F121" s="3">
+      <c r="E124" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F124" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G124" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J124" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="K124" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L124" s="1">
+        <f>6*4-1</f>
+        <v>23</v>
+      </c>
+      <c r="M124" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N124" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O124" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P124" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q124" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R124" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S124" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T124" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U124" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="E125" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F125" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="G125" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J125" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="K125" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L125" s="1">
+        <f>7*4-1</f>
+        <v>27</v>
+      </c>
+      <c r="M125" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N125" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O125" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P125" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q125" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R125" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S125" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T125" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U125" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="E126" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F126" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="G126" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="J126" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="K126" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L126" s="1">
+        <f>8*4-1</f>
+        <v>31</v>
+      </c>
+      <c r="M126" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N126" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O126" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P126" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q126" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="R126" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="S126" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T126" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U126" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="E127" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F127" s="2">
         <v>9.0</v>
       </c>
-      <c r="G121" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I121" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J121" s="3">
+      <c r="G127" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J127" s="2">
         <v>5.0</v>
       </c>
-      <c r="K121" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L121" s="1">
+      <c r="K127" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L127" s="1">
         <f>4*9-1</f>
         <v>35</v>
       </c>
-      <c r="M121" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N121" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O121" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P121" s="1">
+      <c r="M127" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N127" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O127" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P127" s="1">
         <v>42.0</v>
       </c>
-      <c r="Q121" s="1">
+      <c r="Q127" s="1">
         <v>15.0</v>
       </c>
-      <c r="R121" s="1">
+      <c r="R127" s="1">
         <v>39.0</v>
       </c>
-      <c r="S121" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T121" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U121" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="E122" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F122" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G122" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I122" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J122" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="K122" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L122" s="3">
+      <c r="S127" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T127" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U127" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="E128" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F128" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G128" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J128" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="K128" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L128" s="2">
         <v>39.0</v>
       </c>
-      <c r="M122" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N122" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O122" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P122" s="1">
+      <c r="M128" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N128" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O128" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P128" s="1">
         <v>42.0</v>
       </c>
-      <c r="Q122" s="1">
+      <c r="Q128" s="1">
         <v>15.0</v>
       </c>
-      <c r="R122" s="1">
+      <c r="R128" s="1">
         <v>39.0</v>
       </c>
-      <c r="S122" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="U122" s="3" t="s">
+      <c r="S128" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T128" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U128" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -7557,26 +7903,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -8598,143 +8944,143 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
+      <c r="B8" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>50</v>
@@ -8750,7 +9096,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>53</v>
@@ -8758,25 +9104,25 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>56</v>
       </c>
     </row>
